--- a/documents/cogna-process-progress-fields.xlsx
+++ b/documents/cogna-process-progress-fields.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="fields" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>label</t>
   </si>
@@ -38,6 +38,15 @@
     <t>isMultipleField</t>
   </si>
   <si>
+    <t xml:space="preserve">Número do processo</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>CNJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tipo de andamento</t>
   </si>
   <si>
@@ -74,9 +83,6 @@
     <t>Responsável</t>
   </si>
   <si>
-    <t>text</t>
-  </si>
-  <si>
     <t>Endereço</t>
   </si>
   <si>
@@ -146,10 +152,19 @@
     <t xml:space="preserve">Agravo Regimental</t>
   </si>
   <si>
+    <t xml:space="preserve">Opção teste 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agravo de Despacho Denegatório de Resp</t>
   </si>
   <si>
+    <t xml:space="preserve">Nova opção para testes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agravo de Despacho Denegatório de Rext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terceira só pra fazer valer</t>
   </si>
   <si>
     <t xml:space="preserve">Agravo de Instrumento</t>
@@ -397,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -406,9 +421,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -425,7 +437,6 @@
     <xf fontId="1" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,16 +974,18 @@
       <c r="C2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="b">
         <v>1</v>
@@ -983,7 +996,7 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>10</v>
@@ -997,189 +1010,187 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C8" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F9" s="4"/>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="5" t="s">
         <v>18</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F10" s="4"/>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F11" s="4"/>
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="F12" s="4"/>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C13" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C14" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C15" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C16" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -1188,99 +1199,101 @@
         <v>24</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C17" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="F17" s="4"/>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C18" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="4" t="b">
-        <v>0</v>
-      </c>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C19" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C20" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C21" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C22" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C23" s="4" t="b">
         <v>1</v>
@@ -1291,10 +1304,10 @@
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C24" s="4" t="b">
         <v>1</v>
@@ -1305,10 +1318,10 @@
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C25" s="4" t="b">
         <v>1</v>
@@ -1319,10 +1332,10 @@
     </row>
     <row r="26" ht="14.25">
       <c r="A26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>16</v>
+        <v>31</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C26" s="4" t="b">
         <v>1</v>
@@ -1333,17 +1346,15 @@
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>32</v>
-      </c>
+      <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
     </row>
@@ -1352,36 +1363,36 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C28" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="E28" s="4"/>
-      <c r="F28" s="4" t="b">
-        <v>1</v>
-      </c>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C29" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D29" s="4"/>
-      <c r="E29" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="4" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>7</v>
@@ -1391,59 +1402,67 @@
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="6"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C32" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="6"/>
+      <c r="F32" s="5"/>
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C33" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="6"/>
+      <c r="F33" s="5"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="7"/>
+      <c r="A34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="5"/>
     </row>
     <row r="35" ht="14.25">
       <c r="A35" s="1"/>
@@ -1451,7 +1470,7 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="7"/>
+      <c r="F35" s="6"/>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="1"/>
@@ -1459,7 +1478,7 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="7"/>
+      <c r="F36" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1476,449 +1495,549 @@
     <col customWidth="1" min="1" max="1" style="1" width="54.57421875"/>
     <col customWidth="1" min="2" max="2" style="1" width="37.57421875"/>
     <col customWidth="1" min="3" max="3" style="1" width="37.140625"/>
-    <col customWidth="1" min="4" max="4" style="1" width="26.8515625"/>
+    <col customWidth="1" min="4" max="4" style="1" width="60.57421875"/>
     <col customWidth="1" min="5" max="5" style="1" width="26.57421875"/>
     <col min="6" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1">
-      <c r="A1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="A1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>40</v>
       </c>
+      <c r="D1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
-        <v>41</v>
+      <c r="A2" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
-        <v>42</v>
+      <c r="A3" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="s">
-        <v>43</v>
+      <c r="A4" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="s">
-        <v>44</v>
+      <c r="A5" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="D5" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="s">
-        <v>45</v>
+      <c r="A6" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="D6" s="8" t="s">
+        <v>50</v>
+      </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="s">
-        <v>46</v>
+      <c r="A7" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="s">
-        <v>47</v>
+      <c r="A8" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="D8" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="s">
-        <v>48</v>
+      <c r="A9" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="D9" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="s">
-        <v>49</v>
+      <c r="A10" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="D10" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="s">
-        <v>50</v>
+      <c r="A11" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="D11" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="s">
-        <v>51</v>
+      <c r="A12" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="D12" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="s">
-        <v>52</v>
+      <c r="A13" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="D13" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="s">
-        <v>53</v>
+      <c r="A14" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="s">
-        <v>54</v>
+      <c r="A15" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
       <c r="E15" s="4"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="s">
-        <v>55</v>
+      <c r="A16" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="D16" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="s">
-        <v>56</v>
+      <c r="A17" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="D17" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="s">
-        <v>57</v>
+      <c r="A18" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="D18" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="s">
-        <v>58</v>
+      <c r="A19" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="D19" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="s">
-        <v>59</v>
+      <c r="A20" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+      <c r="D20" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="E20" s="4"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="s">
-        <v>60</v>
+      <c r="A21" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="D21" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="E21" s="4"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="s">
-        <v>61</v>
+      <c r="A22" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
+      <c r="D22" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="s">
-        <v>62</v>
+      <c r="A23" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="D23" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="s">
-        <v>63</v>
+      <c r="A24" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+      <c r="D24" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="s">
-        <v>64</v>
+      <c r="A25" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="D25" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="s">
-        <v>65</v>
+      <c r="A26" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="D26" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="s">
-        <v>66</v>
+      <c r="A27" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="D27" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="s">
-        <v>67</v>
+      <c r="A28" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="D28" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="E28" s="4"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="s">
-        <v>68</v>
+      <c r="A29" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="D29" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="s">
-        <v>69</v>
+      <c r="A30" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="D30" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="s">
-        <v>70</v>
+      <c r="A31" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="D31" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="E31" s="4"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="s">
-        <v>71</v>
+      <c r="A32" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="D32" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="s">
-        <v>72</v>
+      <c r="A33" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="D33" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="E33" s="4"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="s">
-        <v>73</v>
+      <c r="A34" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="D34" s="8" t="s">
+        <v>78</v>
+      </c>
       <c r="E34" s="4"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="s">
-        <v>74</v>
+      <c r="A35" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="D35" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="E35" s="4"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="9" t="s">
-        <v>75</v>
+      <c r="A36" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="D36" s="8" t="s">
+        <v>80</v>
+      </c>
       <c r="E36" s="4"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="9" t="s">
-        <v>76</v>
+      <c r="A37" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="D37" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="E37" s="4"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="9" t="s">
-        <v>77</v>
+      <c r="A38" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
+      <c r="D38" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="E38" s="4"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="9" t="s">
-        <v>78</v>
+      <c r="A39" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="D39" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="E39" s="4"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="9" t="s">
-        <v>79</v>
+      <c r="A40" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
+      <c r="D40" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="E40" s="4"/>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="9" t="s">
-        <v>80</v>
+      <c r="A41" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
+      <c r="D41" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="E41" s="4"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="9" t="s">
-        <v>81</v>
+      <c r="A42" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="D42" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="E42" s="4"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="9" t="s">
-        <v>82</v>
+      <c r="A43" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="D43" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="E43" s="4"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="9" t="s">
-        <v>83</v>
+      <c r="A44" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
+      <c r="D44" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="E44" s="4"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="9" t="s">
-        <v>84</v>
+      <c r="A45" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="D45" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="E45" s="4"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="9" t="s">
-        <v>85</v>
+      <c r="A46" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
+      <c r="D46" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="E46" s="4"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="9" t="s">
-        <v>86</v>
+      <c r="A47" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="D47" s="8" t="s">
+        <v>91</v>
+      </c>
       <c r="E47" s="4"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="9" t="s">
-        <v>87</v>
+      <c r="A48" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+      <c r="D48" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="E48" s="4"/>
     </row>
   </sheetData>
@@ -1940,67 +2059,66 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1">
-      <c r="A1" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>91</v>
+      <c r="A1" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="6"/>
+      <c r="A2" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="6"/>
+      <c r="A3" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="A5" s="11" t="s">
+      <c r="C5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5"/>
+      <c r="D5" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/documents/cogna-process-progress-fields.xlsx
+++ b/documents/cogna-process-progress-fields.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="fields" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
   <si>
     <t>label</t>
   </si>
@@ -38,66 +38,78 @@
     <t>isMultipleField</t>
   </si>
   <si>
+    <t>hasAiSearch</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
     <t xml:space="preserve">Número do processo</t>
   </si>
   <si>
+    <t>lawsuitnumber</t>
+  </si>
+  <si>
+    <t>CNJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de andamento</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>Ocorrencia</t>
+  </si>
+  <si>
+    <t>textarea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentos do andamento</t>
+  </si>
+  <si>
+    <t>fieldarray</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criar audiência</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>Audiência</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>Responsável</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
-    <t>CNJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo de andamento</t>
-  </si>
-  <si>
-    <t>select</t>
-  </si>
-  <si>
-    <t>Ocorrencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documentos do andamento</t>
-  </si>
-  <si>
-    <t>fieldarray</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criar audiencia</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>Audiencia</t>
-  </si>
-  <si>
-    <t>Data</t>
+    <t>Endereço</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadastrar Prazo</t>
+  </si>
+  <si>
+    <t>Prazo</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>Responsável</t>
-  </si>
-  <si>
-    <t>Endereço</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cadastrar Prazo</t>
-  </si>
-  <si>
-    <t>Prazo</t>
-  </si>
-  <si>
     <t>Descrição</t>
   </si>
   <si>
-    <t>textarea</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cadastrar Julgamento</t>
   </si>
   <si>
@@ -122,15 +134,18 @@
     <t xml:space="preserve">Previsão de multa</t>
   </si>
   <si>
-    <t>CURRENCE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Documentos OBF</t>
   </si>
   <si>
     <t>Nome</t>
   </si>
   <si>
+    <t>Arquivo</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cumprimento definitivo</t>
   </si>
   <si>
@@ -149,156 +164,1785 @@
     <t xml:space="preserve">Documentos OBF.Tipo</t>
   </si>
   <si>
+    <t>Audiência.Tipo</t>
+  </si>
+  <si>
+    <t>Acompanhamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato Digital</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agravo Regimental</t>
   </si>
   <si>
-    <t xml:space="preserve">Opção teste 1</t>
+    <t>Administrativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo, antes da decisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato da Bolsa (se houver)</t>
   </si>
   <si>
     <t xml:space="preserve">Agravo de Despacho Denegatório de Resp</t>
   </si>
   <si>
-    <t xml:space="preserve">Nova opção para testes</t>
+    <t>Conciliação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo, após decisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrato Financeiro</t>
   </si>
   <si>
     <t xml:space="preserve">Agravo de Despacho Denegatório de Rext</t>
   </si>
   <si>
-    <t xml:space="preserve">Terceira só pra fazer valer</t>
+    <t>Instrução</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acórdão de Embargos Declaratórios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade de Disciplinas</t>
   </si>
   <si>
     <t xml:space="preserve">Agravo de Instrumento</t>
   </si>
   <si>
+    <t>Una</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acórdão do Autor - Mantida Decisão de Improcedência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histórico Escolar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agravo de Instrumento Em Recurso Extraordinário</t>
   </si>
   <si>
+    <t xml:space="preserve">Acórdão do Autor - Mantida Decisão de Procedência em Parte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histórico de Frequência</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alegações Finais</t>
   </si>
   <si>
+    <t xml:space="preserve">Acórdão do Autor - Mantida Decisão de Procedência em Parte - Apenas OBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela Boa Vista</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anexar Ata de Audiência</t>
   </si>
   <si>
+    <t xml:space="preserve">Acórdão do Autor - Provido em Parte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela Serasa Experian</t>
+  </si>
+  <si>
     <t>Apelação</t>
   </si>
   <si>
+    <t xml:space="preserve">Acórdão do Autor - Totalmente Provido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela da situação acadêmica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apresentação de Garantia Em Execução Fiscal</t>
   </si>
   <si>
+    <t xml:space="preserve">Acórdão do Réu - Mantida Decisão de Procedência em Parte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACORDO QUITADO - Extrato Financeiro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arrolar Testemunhas</t>
   </si>
   <si>
+    <t xml:space="preserve">Tela das Bolsas (contendo vigência)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acórdão do Réu - Mantida Decisão de Procedência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACORDO QUITADO - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
     <t>Contestação</t>
   </si>
   <si>
+    <t xml:space="preserve">Tela de solicitação de requerimentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acórdão do Réu - Mantida Decisão de Procedência em Parte - Apenas OBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACORDO QUITADO - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
     <t xml:space="preserve">Contraminuta de Agravo</t>
   </si>
   <si>
+    <t xml:space="preserve">Tela de solicitação de requerimentos (caso curso dependência do TCC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acórdão do Réu - Provido em Parte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACORDO QUITADO - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Contrarrazões de Recurso</t>
   </si>
   <si>
+    <t xml:space="preserve">Tela onde comprove a entrega de documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acórdão do Réu - Totalmente Provido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACORDO QUITADO - Tela sistêmica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Defesa Administrativa</t>
   </si>
   <si>
+    <t xml:space="preserve">Tela que comprove se há andamento do diploma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACORDO QUITADO - Termo de confissão de dívida</t>
+  </si>
+  <si>
     <t xml:space="preserve">Defesa Prévia</t>
   </si>
   <si>
+    <t xml:space="preserve">01º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACRÉSCIMO DE DISCIPLINA - Atestado de matrícula</t>
+  </si>
+  <si>
     <t xml:space="preserve">Despacho Decisório</t>
   </si>
   <si>
+    <t xml:space="preserve">02º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agravo em Recurso Especial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACRÉSCIMO DE DISCIPLINA - Grade e histórico</t>
+  </si>
+  <si>
     <t xml:space="preserve">Elaborar Documentação</t>
   </si>
   <si>
+    <t xml:space="preserve">03º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agravo em Recurso Extraordinário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSÊNCIA DE MATRÍCULA - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
     <t xml:space="preserve">Embargos Infringentes</t>
   </si>
   <si>
+    <t xml:space="preserve">04º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aguardando Realização de Audiência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSÊNCIA DE MATRÍCULA - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Embargos de Declaração</t>
   </si>
   <si>
+    <t xml:space="preserve">05º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSÊNCIA DE MATRÍCULA - Tela sistêmica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Embargos à Execução</t>
   </si>
   <si>
+    <t xml:space="preserve">06º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alegações Finais / Memorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSÊNCIA DE MATRÍCULA - Áudio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Embargos à Execução de Sentença</t>
   </si>
   <si>
+    <t xml:space="preserve">07º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t>Alvará</t>
+  </si>
+  <si>
+    <t>AVCB</t>
+  </si>
+  <si>
     <t xml:space="preserve">Especificação de Provas</t>
   </si>
   <si>
+    <t xml:space="preserve">08º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t>Arquivamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite de obra</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exceção de Pré-executividade</t>
   </si>
   <si>
+    <t xml:space="preserve">09º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audiência Designada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo Coletivo de Banco de Horas dos últimos 05 anos</t>
+  </si>
+  <si>
     <t>Impugnação</t>
   </si>
   <si>
+    <t xml:space="preserve">10º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audiência Realizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo Coletivo de Horas In Itinere dos últimos 05 anos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Impugnação Ao Valor Da Causa</t>
   </si>
   <si>
+    <t xml:space="preserve">11º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audiência Redesignada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo Coletivo de PLR/PPR dos últimos 03 anos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Indicação de Bem à Penhora</t>
   </si>
   <si>
+    <t xml:space="preserve">12º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ação Distribuída</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo Coletivo de Trabalho para Turnos de Revezamento dos últimos 05 anos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mandado de Segurança</t>
   </si>
   <si>
+    <t xml:space="preserve">13º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baixa Provisória</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo de Confidencialidade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Manifestação de Inconformidade</t>
   </si>
   <si>
+    <t xml:space="preserve">14º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloqueio sem Constrição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo homologado</t>
+  </si>
+  <si>
     <t>Memoriais</t>
   </si>
   <si>
+    <t xml:space="preserve">15º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t>Citação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acordo protocolado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Minuta de Acordo</t>
   </si>
   <si>
+    <t xml:space="preserve">16º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citação Expedida</t>
+  </si>
+  <si>
+    <t>Acórdão</t>
+  </si>
+  <si>
     <t xml:space="preserve">Petição Indicando Provas E Quesitos</t>
   </si>
   <si>
+    <t xml:space="preserve">17º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concluso Para Decisão</t>
+  </si>
+  <si>
     <t xml:space="preserve">Petição de Juntada</t>
   </si>
   <si>
+    <t xml:space="preserve">18º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concluso Para Sentença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agravo de Intrumento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prazo Para Resposta</t>
   </si>
   <si>
+    <t xml:space="preserve">19º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contestação / Defesa</t>
+  </si>
+  <si>
+    <t>Ajuizamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protocolar Peça</t>
   </si>
   <si>
+    <t xml:space="preserve">20º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrarrazões de Apelação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvará Judicial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quesitos E Assistente Técnico</t>
   </si>
   <si>
+    <t xml:space="preserve">21º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvará de Funcionamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso Especial</t>
   </si>
   <si>
+    <t xml:space="preserve">22º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculos - apresentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anexos LPU</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso Especial Para Câmara Superior de Recursos Fiscais</t>
   </si>
   <si>
+    <t xml:space="preserve">23º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculos - impugnação aos cálculos do autor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso Extraordinário</t>
   </si>
   <si>
+    <t xml:space="preserve">24º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculos - impugnação aos cálculos do perito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprovação de Ajuizamento</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso Hierárquico</t>
   </si>
   <si>
+    <t xml:space="preserve">25º Termo Aditivo ao Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculos - para acordo</t>
+  </si>
+  <si>
+    <t>Apólice</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso Inominado</t>
   </si>
   <si>
+    <t xml:space="preserve">Cálculos de liquidação apresentados pelo perito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata de Audiência</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso Ordinário</t>
   </si>
   <si>
+    <t xml:space="preserve">Decisão em Agravo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata de colação</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso Voluntário</t>
   </si>
   <si>
+    <t xml:space="preserve">Decisão em Processo Administrativo</t>
+  </si>
+  <si>
+    <t>Atas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso de Apelação</t>
   </si>
   <si>
+    <t xml:space="preserve">Declínio de Competência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atestado de matrícula</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurso de Revista</t>
   </si>
   <si>
+    <t>Depósito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atestados e documentos previdenciários que comprovem afastamento</t>
+  </si>
+  <si>
     <t>Réplica</t>
   </si>
   <si>
+    <t xml:space="preserve">Desistência da Ação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atos constitutivos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Solicitação de Documentos</t>
   </si>
   <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autorização para Solicitação da Procuração</t>
+  </si>
+  <si>
     <t>Tréplica</t>
   </si>
   <si>
+    <t>Distribuição</t>
+  </si>
+  <si>
+    <t>Autorizações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACRÉSCIMO DE DISCIPLINA - Tela sistêmica</t>
+  </si>
+  <si>
+    <t>Embargos</t>
+  </si>
+  <si>
+    <t>Avaliação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANÁLISE CURRICULAR - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avaliação de Desempenho para fins de PLR/PPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANÁLISE CURRICULAR - Comprovante</t>
+  </si>
+  <si>
+    <t>Benfeitorias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANÁLISE CURRICULAR - Requerimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embargos de Divergência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boletim de Ocorrência, Inquérito Policial, Relatórios Internos etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANÁLISE CURRICULAR - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Especificação de provas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boleto do Prêmio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSÊNCIA DE MATRÍCULA - Documentos</t>
+  </si>
+  <si>
+    <t>Estratégia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT (Comunicação de Acidente do Trabalho)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSÊNCIA DE MATRÍCULA - Extrato Financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exceção de Pré-Executividade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCIR (Certificado de Cadastro do Imóvel Rural)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUSÊNCIA DE MATRÍCULA - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Execução definitiva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CND FGTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Execução provisória</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Cumprimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extinção sem julgamento do mérito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Desbloqueio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impugnação aos Embargos à Execução</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Endereço</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impugnação aos cálculos de liquidação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Entrega de EPI's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicação de Assistente Técnico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Entrega de Vale-Refeição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicação de Preposto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Levantamento de Alvará</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicação de Testemunha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iniciado Cumprimento de Sentença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Redução de Carga Horária (docentes)</t>
+  </si>
+  <si>
+    <t>Intimação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Redução de Classe (Turma)/Extinção do Curso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intimação - Apresentação de cálculos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Requisição do Vale-Transporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intimação - Impugnação aos cálculos do perito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Treinamento de utilização de EPI's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Treinamentos em Geral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juntada de Citação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de depósito do FGTS e da multa de 40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juntada de documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de pagamento das verbas rescisórias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justificativa da alteração de Risco/Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de rejeição do pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laudo Pericial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de retirada do livro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liminar Cumprida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comunicação de dispensa ou pedido de demissão a depender da modalidade da rescisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liminar Deferida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confissão de Dívida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liminar Indeferida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato de Locação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidação sentença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato de Prestação de Serviços</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novo Documento/Informação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato de Sublocação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocorrência Escritório - COM multa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato de Trabalho e Aditivos do Paradigma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocorrência Escritório - SEM multa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato/Estatuto Social/Requerimento de Empresário</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contratos de Trabalho e Aditivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagamento De Execução E Complementos Da Execução</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controle de Frequência do Professor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido De Desconsideração Da Personalidade Jurídica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convenção Coletiva Vigente</t>
+  </si>
+  <si>
+    <t>Perícia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convênio firmado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croqui Localizador do(s) Espaço(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurso Adesivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exame médico demissional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurso Administrativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exame médico demissional e documentos vinculados ao SESMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrato Analítico dos Depósitos na Conta do FGTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrato Serasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extrato de Banco de Horas</t>
+  </si>
+  <si>
+    <t>FAP</t>
+  </si>
+  <si>
+    <t>Revelia</t>
+  </si>
+  <si>
+    <t>FGTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roleta Russa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença Improcedente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Cálculo da Diferença entre contrato X mensalidade/Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença Parcialmente Procedente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Documento de Regularidade de Matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CND INSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença Procedente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CND IPTU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença apenas em OBF - Procedência parcial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Extrato Financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CND ISS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença de Embargos Declaratórios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRANÇA/NEGATIVAÇÃO INDEVIDAS (GERAL) - Documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença de Embargos à Execução Improcedente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRANÇA/NEGATIVAÇÃO INDEVIDAS (GERAL) - Extrato Financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença de Embargos à Execução Parcialmente Procedente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulário de Assinaturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRANÇA/NEGATIVAÇÃO INDEVIDAS (GERAL) - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença de Embargos à Execução Procedente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulário de Prestação de Contas ou Comprovante de Reembolso de Despesas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRANÇA/NEGATIVAÇÃO INDEVIDAS (GERAL) - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença de Extinção do Processo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulário de Solicitação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRANÇA/NEGATIVAÇÃO INDEVIDAS (GERAL) - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença de Homologação do Acordo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulário de solicitação de endosso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBRANÇA/NEGATIVAÇÃO INDEVIDAS (GERAL) - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugestão/Alinhamento Jurídico Interno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulário de solicitação de endosso ASSINADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLAÇÃO DE GRAU - Ata de colação</t>
+  </si>
+  <si>
+    <t>Suspensão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulário do Endosso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLAÇÃO DE GRAU - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trânsito em Julgado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fórum Estadual (domicílio a Parte e local do Imóvel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLAÇÃO DE GRAU - Histórico escolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gfip - Preparo Recursal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLAÇÃO DE GRAU - Requerimento</t>
+  </si>
+  <si>
+    <t>Gps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLAÇÃO DE GRAU - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impugnação de cálculos - Reclamante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário dos agentes comerciais (Remuneração Variável)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impugnação/Manifestação ao Laudo Pericial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carta Fiança</t>
+  </si>
+  <si>
+    <t>Inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carta de Advertência e/ou Suspensão (se houver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carta de Transferência de Local de Trabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justiça do Trabalho de 1ª Instancia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carta de preposição</t>
+  </si>
+  <si>
+    <t>LPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carteira de Trabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartão CNPJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laudo de Insalubridade da Unidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartões de Ponto dos Últimos 5 anos (preferencialmente assinados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laudo de Periculosidade da Unidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certidão Fórum Estadual (domicílio a Parte e local do Imóvel) - processos cíveis, criminais, fiscais municipais, estaduais, falência e recuperação judicial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laudo de Vistoria e Registro Fotográfico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certidão Justiça Federal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laudo do Coordenador do Curso ou de Estágio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certidão Justiça do Trabalho de 1ª Instancia (domicílio a Parte e local do Imóvel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licença Ambiental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certidão Negativa de Débitos Trabalhistas (CNDT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licença Sanitária</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certidão de Uso e Ocupação de Solo</t>
+  </si>
+  <si>
+    <t>Liminar</t>
+  </si>
+  <si>
+    <t>Certificado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lista de benfeitorias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificado de inclusão do imóvel</t>
+  </si>
+  <si>
+    <t>Minuta</t>
+  </si>
+  <si>
+    <t>Certificados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minuta de Acordo Protocolado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certificação de Aprovação dos EPI's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minuta de endosso apólice de seguro</t>
+  </si>
+  <si>
+    <t>Certificações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTAS/ACADÊMICO - Documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chave Conectividade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTAS/ACADÊMICO - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check List BTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTAS/ACADÊMICO - Histórico escolar/Provas/Trabalhos</t>
+  </si>
+  <si>
+    <t>Checklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTAS/ACADÊMICO - Provas e Trabalhos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist BTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTAS/ACADÊMICO - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist DTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTAS/ACADÊMICO - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist jurídico</t>
+  </si>
+  <si>
+    <t>Outros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Contrato</t>
+  </si>
+  <si>
+    <t>Comodato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Cálculo detalhado do saldo PEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compromisso para Implemento de Benfeitorias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Documentos</t>
+  </si>
+  <si>
+    <t>Comprovante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Extrato Financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprovante de Bloqueio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Tela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTITUIÇÃO DE MENSALIDADE - Documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTITUIÇÃO DE MENSALIDADE - Extrato Financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTITUIÇÃO DE MENSALIDADE - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTITUIÇÃO DE MENSALIDADE - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTITUIÇÃO DE MENSALIDADE - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTITUIÇÃO DE MENSALIDADE - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RG E CPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recibo para levantamento do Seguro Desemprego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recibos de Férias dos Últimos 5 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Tela sistêmica/ata de prova/Prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Tela sistêmica/histórico escolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comunicação de dispensa ou pedido de demissão a depender da modalidade da rescisão;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANCAMENTO/CANCELAMENTO DE MATRÍCULA - Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANCAMENTO/CANCELAMENTO DE MATRÍCULA - Cálculo da Multa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANCAMENTO/CANCELAMENTO DE MATRÍCULA - Documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingência - Acórdão RO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANCAMENTO/CANCELAMENTO DE MATRÍCULA - Extrato Financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingência - Acórdão RR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR MENSALIDADE - Comprovante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingência - Embargos de Declaração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR MENSALIDADE - Provas e lista de presença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingência - Inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR MENSALIDADE - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingência - Sentença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check list jurídico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contra Notificação - Vendedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comprovante pagamento ITR dos últimos 5 anos</t>
+  </si>
+  <si>
+    <t>Contrato</t>
+  </si>
+  <si>
+    <t>áudio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato Empresa Terceirizada/Polo Parceiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato FINU/PMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato Suporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato com a Operadora de Plano de Saúde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrato de Empreitada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croqui delimitado do Espaço Locado (quando contratação parcial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculo da Diferença entre contrato X mensalidade/Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculo da Multa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculo de Liquidação - Reclamada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculo de atualização do saldo remanescente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálculo detalhado do saldo PEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cópia do ASO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cópia do Processo Administrativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCONTO/BOLSA - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCONTO/BOLSA - Comprovante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCONTO/BOLSA - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIPLOMA - Ata de colação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIPLOMA - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIPLOMA - Comprovante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIPLOMA - Histórico escolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIPLOMA - Provas e lista de presença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIPLOMA - Tela sistêmica</t>
+  </si>
+  <si>
+    <t>Darf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisão/Intimação de pagamento</t>
+  </si>
+  <si>
+    <t>Defesa</t>
+  </si>
+  <si>
+    <t>Distrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento de Regularidade de Matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documento suporte cessão de direitos creditórios</t>
+  </si>
+  <si>
+    <t>Documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentos Anexados à Inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentos Pessoais (RG e CPF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentos de Evidência da Justa Causa</t>
+  </si>
+  <si>
+    <t>Dossiê</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail Externo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail Interno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENADE - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENADE - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - Avaliação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - Convênio firmado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - Grade e histórico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - Relatórios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - Resultado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - Termo de Compromisso de Estágio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTÁGIO - laudo do Coordenador do Curso ou de Estágio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embargos à Execução Fiscal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endosso de atualização (aniversário) de apólice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escritura de compra e venda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escritura de doação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espelho de IPTU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espelho de Ponto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimativa de custo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exame médico demissional e documentos vinculados ao SESMT (atestados, afastamento e etc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - TELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIES - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ficha de Evolução Salarial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ficha de Evolução Salarial do Paradigma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ficha de Registro/Ficha Docente</t>
+  </si>
+  <si>
+    <t>Formulário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulário - Opção (ou não) pelo plano de saúde quando da rescisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulário DLT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fórum Estadual (domicílio a Parte e local do Imóvel) - processos cíveis, criminais, fiscais municipais, estaduais, falência e recuperação judicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade e histórico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gru - Custas Processuais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guia Comprobatória do Recolhimento da Contribuição Assistencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guia Comprobatória do Recolhimento do Imposto Sindical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guia de Pagamento</t>
+  </si>
+  <si>
+    <t>Habite-se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histórico de afastamentos da reclamante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histórico escolar/Provas/Trabalhos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holerites dos Últimos 5 anos/ Ficha financeira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impugnação de cálculos - Periciais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurisprudência STF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurisprudência STJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurisprudência TJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurisprudência TST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justiça Federal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justiça do Trabalho de 1ª Instancia (domicílio a Parte e local do Imóvel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATÉRIA - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATÉRIA - Tela sistêmica</t>
+  </si>
+  <si>
+    <t>Manifestação</t>
+  </si>
+  <si>
+    <t>Matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrícula Imóvel dado em Caução</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrícula do Imóvel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memorando de Entendimentos</t>
+  </si>
+  <si>
+    <t>Memorandos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memorial Descritivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTAS/ACADÊMICO - Tela sistêmica</t>
+  </si>
+  <si>
+    <t>Negociação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota Fiscal</t>
+  </si>
+  <si>
+    <t>Notificação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notificação - Vendedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notificação / Intimação</t>
+  </si>
+  <si>
+    <t>Notificações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objeto e Pé e/ou Relatório emitido pelo advogado patrono das demandas</t>
+  </si>
+  <si>
+    <t>Orçamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orçamento da obra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orçamento da obra pós vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEP - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMT/FINU - Contrato FINU/PMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMT/FINU - Documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMT/FINU - Extrato Financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMT/FINU - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMT/FINU - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMT/FINU - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMT/FINU - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTAL DO ALUNO - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTAL DO ALUNO - Extrato Serasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTAL DO ALUNO - Extrato financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTAL DO ALUNO - Provas e lista de presença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTAL DO ALUNO - Tela sistêmica</t>
+  </si>
+  <si>
+    <t>PPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petição Inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petições Diversas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planilha de Informações de seguro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planilha/Extrato de RVV (Remuneração Variável)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Política Interna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Linha de Argumentação</t>
+  </si>
+  <si>
+    <t>Procuração</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procuração Assinada Digitalizada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projeto Aprovado</t>
+  </si>
+  <si>
+    <t>Projetos</t>
+  </si>
+  <si>
+    <t>Proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposta Comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provas e Trabalhos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provas e lista de presença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quadra Fiscal</t>
+  </si>
+  <si>
+    <t>Quesitos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quesitos e Indicação de Assistentes Técnicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECONHECIMENTO DE CURSO PELO MEC - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECONHECIMENTO DE CURSO PELO MEC - Comprovante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECONHECIMENTO DE CURSO PELO MEC - Histórico escolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECONHECIMENTO DE CURSO PELO MEC - Provas e lista de presença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECONHECIMENTO DE CURSO PELO MEC - Requerimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECONHECIMENTO DE CURSO PELO MEC - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESTITUIÇÃO DE MENSALIDADE - Comprovante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recibos de Pagamento</t>
+  </si>
+  <si>
+    <t>Reconvenção</t>
+  </si>
+  <si>
+    <t>Recurso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurso Especial/Extraordinário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório Gerencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório de Auditoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório de Viagens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório do CENSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório fotográfico</t>
+  </si>
+  <si>
+    <t>Relatórios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatórios - Fichas - Atestados Médicos</t>
+  </si>
+  <si>
+    <t>Requerimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t>Rescisão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resposta aos questionamentos</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se Imóvel Rural, CCIR (Certificado de Cadastro do Imóvel Rural)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se Imóvel Rural, CND ITR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se Imóvel Rural, comprovante pagamento ITR dos últimos 5 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se Imóvel Urbano, CND IPTU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se Imóvel Urbano, Espelho de IPTU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se possuir a Justo Título, cópia dos documentos que justifiquem a posse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro Garantia</t>
+  </si>
+  <si>
+    <t>Sentença</t>
+  </si>
+  <si>
+    <t>Substabelecimento</t>
+  </si>
+  <si>
+    <t>TAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Comprovante de retirada do livro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Documentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Extrato Financeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXA DE SERVIÇO - Tela sistêmica/ata de prova/ Prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANCAMENTO/CANCELAMENTO DE MATRÍCULA - Histórico escolar/Provas/Lista de frequência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANCAMENTO/CANCELAMENTO DE MATRÍCULA - Requerimento de Matrícula/Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANCAMENTO/CANCELAMENTO DE MATRÍCULA - Requerimento ou tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANCAMENTO/CANCELAMENTO DE MATRÍCULA - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSFERÊNCIA - Atestado de matrícula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSFERÊNCIA - Comprovante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSFERÊNCIA - Provas e lista de presença</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSFERÊNCIA - Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRCT complementar TRCT homologado e assinado (Termo de Rescisão do Contrato de Trabalho)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRCT homologado e assinado (Termo de Rescisão do Contrato de Trabalho)</t>
+  </si>
+  <si>
+    <t>Tela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela sistêmica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela sistêmica/ata de prova/ Prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tela sistêmica/histórico escolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo Aditivo ao Comodato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo Aditivo ao Contrato de Locação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo Aditivo ao Contrato de Prestação de Serviços</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo Aditivo ao Contrato de Sublocação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo Vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo de Compromisso de Estágio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo de Desconto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo de Homologação de Acordo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo de acordo comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo de confissão de dívida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termo de negociação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termos de Adesão ao Convênio Médico</t>
+  </si>
+  <si>
+    <t>Transcrição</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR MENSALIDADE - Atestado de matrícula</t>
+  </si>
+  <si>
     <t>fieldKey</t>
   </si>
   <si>
@@ -330,19 +1974,28 @@
   </si>
   <si>
     <t>CADASTRAR_JULGAMENTO</t>
-  </si>
-  <si>
-    <t>AUDIENCIA.TIPO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -354,17 +2007,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11.000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.000000"/>
       <color theme="1" tint="0"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10.500000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1" tint="0"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -409,37 +2087,62 @@
       <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
+    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="3" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -941,7 +2644,7 @@
     <col customWidth="1" min="3" max="3" style="1" width="20.00390625"/>
     <col customWidth="1" min="4" max="4" style="1" width="20.421875"/>
     <col customWidth="1" min="5" max="5" style="1" width="30.421875"/>
-    <col customWidth="1" min="6" max="6" width="20.421875"/>
+    <col customWidth="1" min="6" max="8" width="20.421875"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="15">
@@ -963,29 +2666,39 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4"/>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
+      <c r="A3" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="b">
         <v>1</v>
@@ -993,13 +2706,17 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
+      <c r="G3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
+      <c r="A4" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="b">
         <v>1</v>
@@ -1007,13 +2724,17 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
+      <c r="G4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="b">
         <v>1</v>
@@ -1021,29 +2742,37 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
+      <c r="G5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" s="4"/>
+      <c r="G6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
+      <c r="A7" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="b">
         <v>1</v>
@@ -1051,13 +2780,17 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
+      <c r="G7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="4" t="s">
-        <v>17</v>
+      <c r="A8" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="b">
         <v>1</v>
@@ -1067,77 +2800,97 @@
       <c r="F8" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F9" s="4"/>
+      <c r="G9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="4" t="s">
-        <v>18</v>
+      <c r="A10" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F10" s="4"/>
+      <c r="G10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F11" s="4"/>
+      <c r="G11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="4" t="s">
-        <v>21</v>
+      <c r="A12" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C12" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F12" s="4"/>
+      <c r="G12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="4" t="s">
-        <v>22</v>
+      <c r="A13" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C13" s="4" t="b">
         <v>1</v>
@@ -1145,13 +2898,17 @@
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
+      <c r="G13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4" t="b">
         <v>1</v>
@@ -1161,61 +2918,77 @@
       <c r="F14" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C15" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F15" s="4"/>
+      <c r="G15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F16" s="4"/>
+      <c r="G16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C17" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F17" s="4"/>
+      <c r="G17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
+      <c r="A18" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C18" s="4" t="b">
         <v>1</v>
@@ -1223,13 +2996,17 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
+      <c r="G18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="4" t="s">
-        <v>27</v>
+      <c r="A19" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C19" s="4" t="b">
         <v>1</v>
@@ -1239,61 +3016,77 @@
       <c r="F19" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="G19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C20" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F20" s="4"/>
+      <c r="G20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C21" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F21" s="4"/>
+      <c r="G21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F22" s="4"/>
+      <c r="G22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="4" t="s">
-        <v>28</v>
+      <c r="A23" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C23" s="4" t="b">
         <v>1</v>
@@ -1301,13 +3094,17 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
+      <c r="G23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="4" t="s">
-        <v>29</v>
+      <c r="A24" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C24" s="4" t="b">
         <v>1</v>
@@ -1315,13 +3112,17 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
+      <c r="G24" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="4" t="s">
-        <v>30</v>
+      <c r="A25" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C25" s="4" t="b">
         <v>1</v>
@@ -1329,13 +3130,17 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
+      <c r="G25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="4" t="s">
-        <v>31</v>
+      <c r="A26" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C26" s="4" t="b">
         <v>1</v>
@@ -1343,13 +3148,17 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
+      <c r="G26" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="4" t="s">
-        <v>32</v>
+      <c r="A27" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4" t="b">
         <v>1</v>
@@ -1357,29 +3166,35 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
+      <c r="G27" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="4" t="s">
-        <v>33</v>
+      <c r="A28" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C28" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
+      <c r="G28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="4" t="s">
-        <v>35</v>
+      <c r="A29" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C29" s="4" t="b">
         <v>1</v>
@@ -1389,88 +3204,124 @@
       <c r="F29" s="4" t="b">
         <v>1</v>
       </c>
+      <c r="G29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C30" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F30" s="4"/>
+      <c r="G30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C31" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F31" s="4"/>
+      <c r="G31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C32" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="5"/>
+      <c r="E32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="4" t="s">
-        <v>38</v>
+      <c r="A33" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C33" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="4" t="s">
-        <v>39</v>
+      <c r="A34" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C34" s="4" t="b">
         <v>1</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="A35" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="6"/>
+      <c r="G35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="1"/>
@@ -1478,7 +3329,8 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="6"/>
+      <c r="F36" s="9"/>
+      <c r="H36" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1492,553 +3344,3943 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="1" width="54.57421875"/>
-    <col customWidth="1" min="2" max="2" style="1" width="37.57421875"/>
-    <col customWidth="1" min="3" max="3" style="1" width="37.140625"/>
-    <col customWidth="1" min="4" max="4" style="1" width="60.57421875"/>
-    <col customWidth="1" min="5" max="5" style="1" width="26.57421875"/>
-    <col min="6" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="1" max="1" style="1" width="78.421875"/>
+    <col customWidth="1" min="2" max="2" width="37.57421875"/>
+    <col customWidth="1" min="3" max="3" width="85.57421875"/>
+    <col customWidth="1" min="4" max="4" width="69.140625"/>
+    <col customWidth="1" min="5" max="5" width="25.7109375"/>
+    <col customWidth="1" min="6" max="6" width="26.57421875"/>
+    <col min="7" max="7" width="9.140625"/>
+    <col min="8" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1">
-      <c r="A1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>42</v>
+      <c r="B1" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="4"/>
+      <c r="A2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="4"/>
+      <c r="A3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="12"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="12"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="12"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="12"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="8" t="s">
+      <c r="B16" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="12"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="12"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="12"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="12"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" s="12"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="12"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="12"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="12"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" s="12"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" s="12"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="12"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="12"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E30" s="12"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E31" s="12"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E32" s="12"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="s">
+      <c r="C33" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="12"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" s="12"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E35" s="12"/>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" s="12"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" s="12"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" s="12"/>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" s="12"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="12"/>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" s="12"/>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" s="12"/>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="12"/>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" s="12"/>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E46" s="12"/>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="12"/>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E48" s="12"/>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="E51" s="6"/>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="A54" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="E54" s="6"/>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="E55" s="6"/>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E56" s="6"/>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E57" s="6"/>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C58" s="4"/>
+      <c r="D58" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E58" s="6"/>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E59" s="6"/>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" s="6"/>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E61" s="6"/>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E62" s="6"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" s="6"/>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="A64" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E64" s="6"/>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E65" s="6"/>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E66" s="6"/>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="A67" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E67" s="6"/>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="A68" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C68" s="4"/>
+      <c r="D68" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E68" s="6"/>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="A69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C69" s="4"/>
+      <c r="D69" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" s="6"/>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="A70" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C70" s="4"/>
+      <c r="D70" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E70" s="6"/>
+    </row>
+    <row r="71" ht="14.25">
+      <c r="A71" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E71" s="6"/>
+    </row>
+    <row r="72" ht="14.25">
+      <c r="A72" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E72" s="6"/>
+    </row>
+    <row r="73" ht="14.25">
+      <c r="A73" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C73" s="4"/>
+      <c r="D73" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E73" s="6"/>
+    </row>
+    <row r="74" ht="14.25">
+      <c r="A74" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C74" s="4"/>
+      <c r="D74" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E74" s="6"/>
+    </row>
+    <row r="75" ht="14.25">
+      <c r="A75" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="C75" s="4"/>
+      <c r="D75" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E75" s="6"/>
+    </row>
+    <row r="76" ht="14.25">
+      <c r="A76" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="E76" s="6"/>
+    </row>
+    <row r="77" ht="14.25">
+      <c r="A77" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E77" s="6"/>
+    </row>
+    <row r="78" ht="14.25">
+      <c r="A78" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E78" s="6"/>
+    </row>
+    <row r="79" ht="14.25">
+      <c r="A79" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="E79" s="6"/>
+    </row>
+    <row r="80" ht="14.25">
+      <c r="A80" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C80" s="4"/>
+      <c r="D80" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="E80" s="6"/>
+    </row>
+    <row r="81" ht="14.25">
+      <c r="A81" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="D81" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E81" s="6"/>
+    </row>
+    <row r="82" ht="14.25">
+      <c r="A82" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="D82" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E82" s="6"/>
+    </row>
+    <row r="83" ht="14.25">
+      <c r="A83" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="D83" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E83" s="6"/>
+    </row>
+    <row r="84" ht="14.25">
+      <c r="A84" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="C84" s="4"/>
+      <c r="D84" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="E84" s="6"/>
+    </row>
+    <row r="85" ht="14.25">
+      <c r="A85" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C85" s="4"/>
+      <c r="D85" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="E85" s="6"/>
+    </row>
+    <row r="86" ht="14.25">
+      <c r="A86" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C86" s="4"/>
+      <c r="D86" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E86" s="6"/>
+    </row>
+    <row r="87" ht="14.25">
+      <c r="A87" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C87" s="4"/>
+      <c r="D87" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E87" s="6"/>
+    </row>
+    <row r="88" ht="14.25">
+      <c r="A88" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="C88" s="4"/>
+      <c r="D88" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E88" s="6"/>
+    </row>
+    <row r="89" ht="14.25">
+      <c r="A89" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B89" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" ht="14.25">
-      <c r="A36" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" ht="14.25">
-      <c r="A37" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" ht="14.25">
-      <c r="A38" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" ht="14.25">
-      <c r="A39" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" ht="14.25">
-      <c r="A40" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" ht="14.25">
-      <c r="A41" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" ht="14.25">
-      <c r="A42" s="8" t="s">
+      <c r="C89" s="4"/>
+      <c r="D89" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="E89" s="6"/>
+    </row>
+    <row r="90" ht="14.25">
+      <c r="A90" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C90" s="4"/>
+      <c r="D90" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="E90" s="6"/>
+    </row>
+    <row r="91" ht="14.25">
+      <c r="A91" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C91" s="4"/>
+      <c r="D91" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E91" s="6"/>
+    </row>
+    <row r="92" ht="14.25">
+      <c r="A92" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="C92" s="4"/>
+      <c r="D92" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E92" s="6"/>
+    </row>
+    <row r="93" ht="14.25">
+      <c r="A93" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C93" s="4"/>
+      <c r="D93" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="E93" s="6"/>
+    </row>
+    <row r="94" ht="14.25">
+      <c r="A94" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="C94" s="4"/>
+      <c r="D94" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E94" s="6"/>
+    </row>
+    <row r="95" ht="14.25">
+      <c r="A95" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="C95" s="4"/>
+      <c r="D95" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="E95" s="6"/>
+    </row>
+    <row r="96" ht="14.25">
+      <c r="A96" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C96" s="4"/>
+      <c r="D96" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E96" s="6"/>
+    </row>
+    <row r="97" ht="14.25">
+      <c r="A97" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="C97" s="4"/>
+      <c r="D97" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="E97" s="6"/>
+    </row>
+    <row r="98" ht="14.25">
+      <c r="A98" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="C98" s="4"/>
+      <c r="D98" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E98" s="6"/>
+    </row>
+    <row r="99" ht="14.25">
+      <c r="A99" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="C99" s="4"/>
+      <c r="D99" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="E99" s="6"/>
+    </row>
+    <row r="100" ht="14.25">
+      <c r="A100" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="C100" s="4"/>
+      <c r="D100" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="E100" s="6"/>
+    </row>
+    <row r="101" ht="14.25">
+      <c r="A101" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C101" s="4"/>
+      <c r="D101" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="E101" s="6"/>
+    </row>
+    <row r="102" ht="14.25">
+      <c r="A102" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C102" s="4"/>
+      <c r="D102" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="E102" s="6"/>
+    </row>
+    <row r="103" ht="14.25">
+      <c r="A103" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C103" s="4"/>
+      <c r="D103" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E103" s="6"/>
+    </row>
+    <row r="104" ht="14.25">
+      <c r="A104" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="C104" s="4"/>
+      <c r="D104" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E104" s="6"/>
+    </row>
+    <row r="105" ht="14.25">
+      <c r="A105" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C105" s="4"/>
+      <c r="D105" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E105" s="6"/>
+    </row>
+    <row r="106" ht="14.25">
+      <c r="A106" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C106" s="4"/>
+      <c r="D106" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="E106" s="6"/>
+    </row>
+    <row r="107" ht="14.25">
+      <c r="A107" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E107" s="6"/>
+    </row>
+    <row r="108" ht="14.25">
+      <c r="A108" s="4"/>
+      <c r="B108" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="C108" s="4"/>
+      <c r="D108" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="E108" s="6"/>
+    </row>
+    <row r="109" ht="14.25">
+      <c r="A109" s="4"/>
+      <c r="B109" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C109" s="4"/>
+      <c r="D109" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E109" s="6"/>
+    </row>
+    <row r="110" ht="14.25">
+      <c r="A110" s="4"/>
+      <c r="B110" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="C110" s="4"/>
+      <c r="D110" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E110" s="6"/>
+    </row>
+    <row r="111" ht="14.25">
+      <c r="A111" s="4"/>
+      <c r="B111" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="C111" s="4"/>
+      <c r="D111" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="E111" s="6"/>
+    </row>
+    <row r="112" ht="14.25">
+      <c r="A112" s="4"/>
+      <c r="B112" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="C112" s="4"/>
+      <c r="D112" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E112" s="6"/>
+    </row>
+    <row r="113" ht="14.25">
+      <c r="A113" s="4"/>
+      <c r="B113" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C113" s="4"/>
+      <c r="D113" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="E113" s="6"/>
+    </row>
+    <row r="114" ht="14.25">
+      <c r="A114" s="4"/>
+      <c r="B114" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C114" s="4"/>
+      <c r="D114" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="E114" s="6"/>
+    </row>
+    <row r="115" ht="14.25">
+      <c r="A115" s="4"/>
+      <c r="B115" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="C115" s="4"/>
+      <c r="D115" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="E115" s="6"/>
+    </row>
+    <row r="116" ht="14.25">
+      <c r="A116" s="4"/>
+      <c r="B116" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116" s="4"/>
+      <c r="D116" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E116" s="6"/>
+    </row>
+    <row r="117" ht="14.25">
+      <c r="A117" s="4"/>
+      <c r="B117" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="C117" s="4"/>
+      <c r="D117" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="E117" s="6"/>
+    </row>
+    <row r="118" ht="14.25">
+      <c r="A118" s="4"/>
+      <c r="B118" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="C118" s="4"/>
+      <c r="D118" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="E118" s="6"/>
+    </row>
+    <row r="119" ht="14.25">
+      <c r="A119" s="4"/>
+      <c r="B119" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="C119" s="4"/>
+      <c r="D119" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="E119" s="6"/>
+    </row>
+    <row r="120" ht="14.25">
+      <c r="A120" s="4"/>
+      <c r="B120" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="C120" s="4"/>
+      <c r="D120" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="E120" s="6"/>
+    </row>
+    <row r="121" ht="14.25">
+      <c r="A121" s="4"/>
+      <c r="B121" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C121" s="4"/>
+      <c r="D121" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="E121" s="6"/>
+    </row>
+    <row r="122" ht="14.25">
+      <c r="A122" s="4"/>
+      <c r="B122" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="C122" s="4"/>
+      <c r="D122" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="E122" s="6"/>
+    </row>
+    <row r="123" ht="14.25">
+      <c r="A123" s="4"/>
+      <c r="B123" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="C123" s="4"/>
+      <c r="D123" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="E123" s="6"/>
+    </row>
+    <row r="124" ht="14.25">
+      <c r="A124" s="4"/>
+      <c r="B124" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" s="4"/>
+      <c r="D124" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="E124" s="6"/>
+    </row>
+    <row r="125" ht="14.25">
+      <c r="A125" s="4"/>
+      <c r="B125" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C125" s="4"/>
+      <c r="D125" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="E125" s="6"/>
+    </row>
+    <row r="126" ht="14.25">
+      <c r="A126" s="4"/>
+      <c r="B126" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="C126" s="4"/>
+      <c r="D126" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="E126" s="6"/>
+    </row>
+    <row r="127" ht="14.25">
+      <c r="A127" s="4"/>
+      <c r="B127" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="C127" s="4"/>
+      <c r="D127" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="E127" s="6"/>
+    </row>
+    <row r="128" ht="14.25">
+      <c r="A128" s="4"/>
+      <c r="B128" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="C128" s="4"/>
+      <c r="D128" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="E128" s="6"/>
+    </row>
+    <row r="129" ht="14.25">
+      <c r="A129" s="4"/>
+      <c r="B129" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="C129" s="4"/>
+      <c r="D129" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="E129" s="6"/>
+    </row>
+    <row r="130" ht="14.25">
+      <c r="A130" s="4"/>
+      <c r="B130" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C130" s="4"/>
+      <c r="D130" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="E130" s="6"/>
+    </row>
+    <row r="131" ht="14.25">
+      <c r="A131" s="4"/>
+      <c r="B131" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="C131" s="4"/>
+      <c r="D131" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="E131" s="6"/>
+    </row>
+    <row r="132" ht="14.25">
+      <c r="A132" s="4"/>
+      <c r="B132" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="C132" s="4"/>
+      <c r="D132" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="E132" s="6"/>
+    </row>
+    <row r="133" ht="14.25">
+      <c r="A133" s="4"/>
+      <c r="B133" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="C133" s="4"/>
+      <c r="D133" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="E133" s="6"/>
+    </row>
+    <row r="134" ht="14.25">
+      <c r="A134" s="4"/>
+      <c r="B134" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="C134" s="4"/>
+      <c r="D134" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E134" s="6"/>
+    </row>
+    <row r="135" ht="14.25">
+      <c r="A135" s="4"/>
+      <c r="B135" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="E135" s="6"/>
+    </row>
+    <row r="136" ht="14.25">
+      <c r="A136" s="4"/>
+      <c r="B136" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="C136" s="4"/>
+      <c r="D136" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="E136" s="6"/>
+    </row>
+    <row r="137" ht="14.25">
+      <c r="A137" s="4"/>
+      <c r="B137" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="C137" s="4"/>
+      <c r="D137" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="E137" s="6"/>
+    </row>
+    <row r="138" ht="14.25">
+      <c r="A138" s="4"/>
+      <c r="B138" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="C138" s="4"/>
+      <c r="D138" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="E138" s="6"/>
+    </row>
+    <row r="139" ht="14.25">
+      <c r="A139" s="4"/>
+      <c r="B139" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C139" s="4"/>
+      <c r="D139" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E139" s="6"/>
+    </row>
+    <row r="140" ht="14.25">
+      <c r="A140" s="4"/>
+      <c r="B140" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="C140" s="4"/>
+      <c r="D140" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="E140" s="6"/>
+    </row>
+    <row r="141" ht="14.25">
+      <c r="A141" s="4"/>
+      <c r="B141" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="C141" s="4"/>
+      <c r="D141" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="E141" s="6"/>
+    </row>
+    <row r="142" ht="14.25">
+      <c r="A142" s="4"/>
+      <c r="B142" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E142" s="6"/>
+    </row>
+    <row r="143" ht="14.25">
+      <c r="A143" s="4"/>
+      <c r="B143" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="C143" s="4"/>
+      <c r="D143" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E143" s="6"/>
+    </row>
+    <row r="144" ht="14.25">
+      <c r="A144" s="4"/>
+      <c r="B144" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="C144" s="4"/>
+      <c r="D144" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E144" s="6"/>
+    </row>
+    <row r="145" ht="14.25">
+      <c r="A145" s="4"/>
+      <c r="B145" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="C145" s="4"/>
+      <c r="D145" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="E145" s="6"/>
+    </row>
+    <row r="146" ht="14.25">
+      <c r="A146" s="4"/>
+      <c r="B146" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C146" s="4"/>
+      <c r="D146" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="E146" s="6"/>
+    </row>
+    <row r="147" ht="14.25">
+      <c r="A147" s="4"/>
+      <c r="B147" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="C147" s="4"/>
+      <c r="D147" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E147" s="6"/>
+    </row>
+    <row r="148" ht="14.25">
+      <c r="A148" s="4"/>
+      <c r="B148" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="C148" s="4"/>
+      <c r="D148" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="E148" s="6"/>
+    </row>
+    <row r="149" ht="14.25">
+      <c r="A149" s="4"/>
+      <c r="B149" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="C149" s="4"/>
+      <c r="D149" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E149" s="6"/>
+    </row>
+    <row r="150" ht="14.25">
+      <c r="A150" s="4"/>
+      <c r="B150" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="C150" s="4"/>
+      <c r="D150" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="E150" s="6"/>
+    </row>
+    <row r="151" ht="14.25">
+      <c r="A151" s="4"/>
+      <c r="B151" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="C151" s="4"/>
+      <c r="D151" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E151" s="6"/>
+    </row>
+    <row r="152" ht="14.25">
+      <c r="A152" s="4"/>
+      <c r="B152" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="4"/>
+      <c r="D152" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="E152" s="6"/>
+    </row>
+    <row r="153" ht="14.25">
+      <c r="A153" s="4"/>
+      <c r="B153" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="E153" s="6"/>
+    </row>
+    <row r="154" ht="14.25">
+      <c r="A154" s="4"/>
+      <c r="B154" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="C154" s="4"/>
+      <c r="D154" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E154" s="6"/>
+    </row>
+    <row r="155" ht="14.25">
+      <c r="A155" s="4"/>
+      <c r="B155" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C155" s="4"/>
+      <c r="D155" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="E155" s="6"/>
+    </row>
+    <row r="156" ht="14.25">
+      <c r="A156" s="4"/>
+      <c r="B156" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="C156" s="4"/>
+      <c r="D156" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E156" s="6"/>
+    </row>
+    <row r="157" ht="14.25">
+      <c r="A157" s="4"/>
+      <c r="B157" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="C157" s="4"/>
+      <c r="D157" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E42" s="4"/>
-    </row>
-    <row r="43" ht="14.25">
-      <c r="A43" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E43" s="4"/>
-    </row>
-    <row r="44" ht="14.25">
-      <c r="A44" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44" s="4"/>
-    </row>
-    <row r="45" ht="14.25">
-      <c r="A45" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E45" s="4"/>
-    </row>
-    <row r="46" ht="14.25">
-      <c r="A46" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E46" s="4"/>
-    </row>
-    <row r="47" ht="14.25">
-      <c r="A47" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E47" s="4"/>
-    </row>
-    <row r="48" ht="14.25">
-      <c r="A48" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E48" s="4"/>
+      <c r="E157" s="6"/>
+    </row>
+    <row r="158" ht="14.25">
+      <c r="A158" s="4"/>
+      <c r="B158" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="C158" s="4"/>
+      <c r="D158" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E158" s="6"/>
+    </row>
+    <row r="159" ht="14.25">
+      <c r="A159" s="4"/>
+      <c r="B159" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="C159" s="4"/>
+      <c r="D159" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="E159" s="6"/>
+    </row>
+    <row r="160" ht="14.25">
+      <c r="A160" s="4"/>
+      <c r="B160" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="C160" s="4"/>
+      <c r="D160" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="E160" s="6"/>
+    </row>
+    <row r="161" ht="14.25">
+      <c r="A161" s="4"/>
+      <c r="B161" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C161" s="4"/>
+      <c r="D161" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="E161" s="6"/>
+    </row>
+    <row r="162" ht="14.25">
+      <c r="A162" s="4"/>
+      <c r="B162" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="C162" s="4"/>
+      <c r="D162" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="E162" s="6"/>
+    </row>
+    <row r="163" ht="14.25">
+      <c r="A163" s="4"/>
+      <c r="B163" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="C163" s="4"/>
+      <c r="D163" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="E163" s="6"/>
+    </row>
+    <row r="164" ht="14.25">
+      <c r="A164" s="4"/>
+      <c r="B164" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C164" s="4"/>
+      <c r="D164" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="E164" s="6"/>
+    </row>
+    <row r="165" ht="14.25">
+      <c r="A165" s="4"/>
+      <c r="B165" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="C165" s="4"/>
+      <c r="D165" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="E165" s="6"/>
+    </row>
+    <row r="166" ht="14.25">
+      <c r="A166" s="1"/>
+      <c r="B166" s="15"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="E166" s="9"/>
+    </row>
+    <row r="167" ht="14.25">
+      <c r="A167" s="1"/>
+      <c r="B167" s="15"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="E167" s="9"/>
+    </row>
+    <row r="168" ht="14.25">
+      <c r="A168" s="1"/>
+      <c r="B168" s="15"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="E168" s="9"/>
+    </row>
+    <row r="169" ht="14.25">
+      <c r="A169" s="1"/>
+      <c r="B169" s="15"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="E169" s="9"/>
+    </row>
+    <row r="170" ht="14.25">
+      <c r="A170" s="1"/>
+      <c r="B170" s="15"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E170" s="9"/>
+    </row>
+    <row r="171" ht="14.25">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="E171" s="9"/>
+    </row>
+    <row r="172" ht="14.25">
+      <c r="A172" s="1"/>
+      <c r="B172" s="15"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="E172" s="9"/>
+    </row>
+    <row r="173" ht="14.25">
+      <c r="A173" s="1"/>
+      <c r="B173" s="15"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E173" s="9"/>
+    </row>
+    <row r="174" ht="14.25">
+      <c r="A174" s="1"/>
+      <c r="B174" s="15"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="E174" s="9"/>
+    </row>
+    <row r="175" ht="14.25">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="E175" s="9"/>
+    </row>
+    <row r="176" ht="14.25">
+      <c r="A176" s="1"/>
+      <c r="B176" s="15"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="E176" s="9"/>
+    </row>
+    <row r="177" ht="14.25">
+      <c r="A177" s="1"/>
+      <c r="B177" s="15"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="E177" s="9"/>
+    </row>
+    <row r="178" ht="14.25">
+      <c r="A178" s="1"/>
+      <c r="B178" s="15"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="E178" s="9"/>
+    </row>
+    <row r="179" ht="14.25">
+      <c r="A179" s="1"/>
+      <c r="B179" s="15"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="E179" s="9"/>
+    </row>
+    <row r="180" ht="14.25">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="E180" s="9"/>
+    </row>
+    <row r="181" ht="14.25">
+      <c r="A181" s="1"/>
+      <c r="B181" s="15"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="E181" s="9"/>
+    </row>
+    <row r="182" ht="14.25">
+      <c r="A182" s="1"/>
+      <c r="B182" s="15"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="E182" s="9"/>
+    </row>
+    <row r="183" ht="14.25">
+      <c r="A183" s="1"/>
+      <c r="B183" s="15"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="E183" s="9"/>
+    </row>
+    <row r="184" ht="14.25">
+      <c r="A184" s="1"/>
+      <c r="B184" s="15"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="E184" s="9"/>
+    </row>
+    <row r="185" ht="14.25">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="E185" s="9"/>
+    </row>
+    <row r="186" ht="14.25">
+      <c r="A186" s="1"/>
+      <c r="B186" s="15"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="E186" s="9"/>
+    </row>
+    <row r="187" ht="14.25">
+      <c r="A187" s="1"/>
+      <c r="B187" s="15"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="E187" s="9"/>
+    </row>
+    <row r="188" ht="14.25">
+      <c r="A188" s="1"/>
+      <c r="B188" s="15"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="E188" s="9"/>
+    </row>
+    <row r="189" ht="14.25">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="E189" s="9"/>
+    </row>
+    <row r="190" ht="14.25">
+      <c r="A190" s="1"/>
+      <c r="B190" s="15"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="E190" s="9"/>
+    </row>
+    <row r="191" ht="14.25">
+      <c r="A191" s="1"/>
+      <c r="B191" s="15"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="E191" s="9"/>
+    </row>
+    <row r="192" ht="14.25">
+      <c r="A192" s="1"/>
+      <c r="B192" s="15"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="E192" s="9"/>
+    </row>
+    <row r="193" ht="14.25">
+      <c r="B193" s="1"/>
+      <c r="D193" s="15" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="194" ht="14.25">
+      <c r="B194" s="1"/>
+      <c r="D194" s="15" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="195" ht="14.25">
+      <c r="B195" s="1"/>
+      <c r="D195" s="15" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="196" ht="14.25">
+      <c r="B196" s="1"/>
+      <c r="D196" s="15" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="197" ht="14.25">
+      <c r="B197" s="1"/>
+      <c r="D197" s="15" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="198" ht="14.25">
+      <c r="B198" s="1"/>
+      <c r="D198" s="15" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="199" ht="14.25">
+      <c r="B199" s="1"/>
+      <c r="D199" s="15" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="200" ht="14.25">
+      <c r="B200" s="1"/>
+      <c r="D200" s="15" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="201" ht="14.25">
+      <c r="B201" s="1"/>
+      <c r="D201" s="15" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="202" ht="14.25">
+      <c r="B202" s="1"/>
+      <c r="D202" s="15" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="203" ht="14.25">
+      <c r="B203" s="1"/>
+      <c r="D203" s="15" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="204" ht="14.25">
+      <c r="B204" s="1"/>
+      <c r="D204" s="15" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="205" ht="14.25">
+      <c r="B205" s="1"/>
+      <c r="D205" s="15" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="206" ht="14.25">
+      <c r="B206" s="1"/>
+      <c r="D206" s="15" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="207" ht="14.25">
+      <c r="B207" s="1"/>
+      <c r="D207" s="15" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="208" ht="14.25">
+      <c r="B208" s="1"/>
+      <c r="D208" s="15" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="209" ht="14.25">
+      <c r="B209" s="1"/>
+      <c r="D209" s="15" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="210" ht="14.25">
+      <c r="B210" s="1"/>
+      <c r="D210" s="15" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="211" ht="14.25">
+      <c r="B211" s="1"/>
+      <c r="D211" s="15" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="212" ht="14.25">
+      <c r="B212" s="1"/>
+      <c r="D212" s="15" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="213" ht="14.25">
+      <c r="B213" s="1"/>
+      <c r="D213" s="15" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="214" ht="14.25">
+      <c r="B214" s="1"/>
+      <c r="D214" s="15" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="215" ht="14.25">
+      <c r="B215" s="1"/>
+      <c r="D215" s="15" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="216" ht="14.25">
+      <c r="B216" s="1"/>
+      <c r="D216" s="15" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="217" ht="14.25">
+      <c r="B217" s="1"/>
+      <c r="D217" s="15" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="218" ht="14.25">
+      <c r="B218" s="1"/>
+      <c r="D218" s="15" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="219" ht="14.25">
+      <c r="B219" s="1"/>
+      <c r="D219" s="15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="220" ht="14.25">
+      <c r="B220" s="1"/>
+      <c r="D220" s="15" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="221" ht="14.25">
+      <c r="B221" s="1"/>
+      <c r="D221" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="222" ht="14.25">
+      <c r="B222" s="1"/>
+      <c r="D222" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="223" ht="14.25">
+      <c r="B223" s="1"/>
+      <c r="D223" s="15" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="224" ht="14.25">
+      <c r="B224" s="1"/>
+      <c r="D224" s="15" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="225" ht="14.25">
+      <c r="B225" s="1"/>
+      <c r="D225" s="15" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="226" ht="14.25">
+      <c r="B226" s="1"/>
+      <c r="D226" s="15" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="227" ht="14.25">
+      <c r="B227" s="1"/>
+      <c r="D227" s="15" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="228" ht="14.25">
+      <c r="B228" s="1"/>
+      <c r="D228" s="15" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="229" ht="14.25">
+      <c r="B229" s="1"/>
+      <c r="D229" s="15" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="230" ht="14.25">
+      <c r="B230" s="1"/>
+      <c r="D230" s="15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="231" ht="14.25">
+      <c r="B231" s="1"/>
+      <c r="D231" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="232" ht="14.25">
+      <c r="B232" s="1"/>
+      <c r="D232" s="15" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="233" ht="14.25">
+      <c r="B233" s="1"/>
+      <c r="D233" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="234" ht="14.25">
+      <c r="B234" s="1"/>
+      <c r="D234" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="235" ht="14.25">
+      <c r="B235" s="1"/>
+      <c r="D235" s="15" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="236" ht="14.25">
+      <c r="B236" s="1"/>
+      <c r="D236" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="237" ht="14.25">
+      <c r="B237" s="1"/>
+      <c r="D237" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="238" ht="14.25">
+      <c r="B238" s="1"/>
+      <c r="D238" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="239" ht="14.25">
+      <c r="B239" s="1"/>
+      <c r="D239" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="240" ht="14.25">
+      <c r="B240" s="1"/>
+      <c r="D240" s="15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="241" ht="14.25">
+      <c r="B241" s="1"/>
+      <c r="D241" s="15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="242" ht="14.25">
+      <c r="B242" s="1"/>
+      <c r="D242" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="243" ht="14.25">
+      <c r="B243" s="1"/>
+      <c r="D243" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="244" ht="14.25">
+      <c r="B244" s="1"/>
+      <c r="D244" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="245" ht="14.25">
+      <c r="B245" s="1"/>
+      <c r="D245" s="15" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="246" ht="14.25">
+      <c r="B246" s="1"/>
+      <c r="D246" s="15" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="247" ht="14.25">
+      <c r="B247" s="1"/>
+      <c r="D247" s="15" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="248" ht="14.25">
+      <c r="B248" s="1"/>
+      <c r="D248" s="15" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="249" ht="14.25">
+      <c r="B249" s="1"/>
+      <c r="D249" s="15" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="250" ht="14.25">
+      <c r="B250" s="1"/>
+      <c r="D250" s="15" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="251" ht="14.25">
+      <c r="B251" s="1"/>
+      <c r="D251" s="15" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="252" ht="14.25">
+      <c r="B252" s="1"/>
+      <c r="D252" s="15" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="253" ht="14.25">
+      <c r="B253" s="1"/>
+      <c r="D253" s="15" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="254" ht="14.25">
+      <c r="B254" s="1"/>
+      <c r="D254" s="15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="255" ht="14.25">
+      <c r="B255" s="1"/>
+      <c r="D255" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="256" ht="14.25">
+      <c r="B256" s="1"/>
+      <c r="D256" s="15" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="257" ht="14.25">
+      <c r="B257" s="1"/>
+      <c r="D257" s="15" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="258" ht="14.25">
+      <c r="B258" s="1"/>
+      <c r="D258" s="15" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="259" ht="14.25">
+      <c r="B259" s="1"/>
+      <c r="D259" s="15" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="260" ht="14.25">
+      <c r="B260" s="1"/>
+      <c r="D260" s="15" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="261" ht="14.25">
+      <c r="B261" s="1"/>
+      <c r="D261" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="262" ht="14.25">
+      <c r="B262" s="1"/>
+      <c r="D262" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="263" ht="14.25">
+      <c r="B263" s="1"/>
+      <c r="D263" s="15" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="264" ht="14.25">
+      <c r="B264" s="1"/>
+      <c r="D264" s="15" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="265" ht="14.25">
+      <c r="B265" s="1"/>
+      <c r="D265" s="15" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="266" ht="14.25">
+      <c r="B266" s="1"/>
+      <c r="D266" s="15" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="267" ht="14.25">
+      <c r="B267" s="1"/>
+      <c r="D267" s="15" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="268" ht="14.25">
+      <c r="B268" s="1"/>
+      <c r="D268" s="15" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="269" ht="14.25">
+      <c r="B269" s="1"/>
+      <c r="D269" s="15" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="270" ht="14.25">
+      <c r="B270" s="1"/>
+      <c r="D270" s="15" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="271" ht="14.25">
+      <c r="B271" s="1"/>
+      <c r="D271" s="15" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="272" ht="14.25">
+      <c r="B272" s="1"/>
+      <c r="D272" s="15" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="273" ht="14.25">
+      <c r="B273" s="1"/>
+      <c r="D273" s="15" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="274" ht="14.25">
+      <c r="B274" s="1"/>
+      <c r="D274" s="15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="275" ht="14.25">
+      <c r="B275" s="1"/>
+      <c r="D275" s="15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="276" ht="14.25">
+      <c r="B276" s="1"/>
+      <c r="D276" s="15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="277" ht="14.25">
+      <c r="B277" s="1"/>
+      <c r="D277" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="278" ht="14.25">
+      <c r="B278" s="1"/>
+      <c r="D278" s="15" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="279" ht="14.25">
+      <c r="B279" s="1"/>
+      <c r="D279" s="15" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="280" ht="14.25">
+      <c r="B280" s="1"/>
+      <c r="D280" s="15" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="281" ht="14.25">
+      <c r="B281" s="1"/>
+      <c r="D281" s="15" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="282" ht="14.25">
+      <c r="B282" s="1"/>
+      <c r="D282" s="15" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="283" ht="14.25">
+      <c r="B283" s="1"/>
+      <c r="D283" s="15" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="284" ht="14.25">
+      <c r="B284" s="1"/>
+      <c r="D284" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="285" ht="14.25">
+      <c r="B285" s="1"/>
+      <c r="D285" s="15" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="286" ht="14.25">
+      <c r="B286" s="1"/>
+      <c r="D286" s="15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="287" ht="14.25">
+      <c r="B287" s="1"/>
+      <c r="D287" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="288" ht="14.25">
+      <c r="B288" s="1"/>
+      <c r="D288" s="15" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="289" ht="14.25">
+      <c r="B289" s="1"/>
+      <c r="D289" s="15" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="290" ht="14.25">
+      <c r="B290" s="1"/>
+      <c r="D290" s="15" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="291" ht="14.25">
+      <c r="B291" s="1"/>
+      <c r="D291" s="15" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="292" ht="14.25">
+      <c r="B292" s="1"/>
+      <c r="D292" s="15" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="293" ht="14.25">
+      <c r="B293" s="1"/>
+      <c r="D293" s="15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="294" ht="14.25">
+      <c r="B294" s="1"/>
+      <c r="D294" s="15" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="295" ht="14.25">
+      <c r="B295" s="1"/>
+      <c r="D295" s="15" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="296" ht="14.25">
+      <c r="B296" s="1"/>
+      <c r="D296" s="15" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="297" ht="14.25">
+      <c r="B297" s="1"/>
+      <c r="D297" s="15" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="298" ht="14.25">
+      <c r="B298" s="1"/>
+      <c r="D298" s="15" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="299" ht="14.25">
+      <c r="B299" s="1"/>
+      <c r="D299" s="15" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="300" ht="14.25">
+      <c r="B300" s="1"/>
+      <c r="D300" s="15" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="301" ht="14.25">
+      <c r="B301" s="1"/>
+      <c r="D301" s="15" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="302" ht="14.25">
+      <c r="B302" s="1"/>
+      <c r="D302" s="15" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="303" ht="14.25">
+      <c r="B303" s="1"/>
+      <c r="D303" s="15" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="304" ht="14.25">
+      <c r="B304" s="1"/>
+      <c r="D304" s="15" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="305" ht="14.25">
+      <c r="B305" s="1"/>
+      <c r="D305" s="15" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="306" ht="14.25">
+      <c r="B306" s="1"/>
+      <c r="D306" s="15" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="307" ht="14.25">
+      <c r="B307" s="1"/>
+      <c r="D307" s="15" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="308" ht="14.25">
+      <c r="B308" s="1"/>
+      <c r="D308" s="15" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="309" ht="14.25">
+      <c r="B309" s="1"/>
+      <c r="D309" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="310" ht="14.25">
+      <c r="B310" s="1"/>
+      <c r="D310" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="311" ht="14.25">
+      <c r="B311" s="1"/>
+      <c r="D311" s="15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="312" ht="14.25">
+      <c r="B312" s="1"/>
+      <c r="D312" s="15" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="313" ht="14.25">
+      <c r="B313" s="1"/>
+      <c r="D313" s="15" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="314" ht="14.25">
+      <c r="B314" s="1"/>
+      <c r="D314" s="15" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="315" ht="14.25">
+      <c r="B315" s="1"/>
+      <c r="D315" s="15" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="316" ht="14.25">
+      <c r="B316" s="1"/>
+      <c r="D316" s="15" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="317" ht="14.25">
+      <c r="B317" s="1"/>
+      <c r="D317" s="15" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="318" ht="14.25">
+      <c r="B318" s="1"/>
+      <c r="D318" s="15" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="319" ht="14.25">
+      <c r="B319" s="1"/>
+      <c r="D319" s="15" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="320" ht="14.25">
+      <c r="B320" s="1"/>
+      <c r="D320" s="15" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="321" ht="14.25">
+      <c r="B321" s="1"/>
+      <c r="D321" s="15" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="322" ht="14.25">
+      <c r="B322" s="1"/>
+      <c r="D322" s="15" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="323" ht="14.25">
+      <c r="B323" s="1"/>
+      <c r="D323" s="15" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="324" ht="14.25">
+      <c r="B324" s="1"/>
+      <c r="D324" s="15" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="325" ht="14.25">
+      <c r="B325" s="1"/>
+      <c r="D325" s="15" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="326" ht="14.25">
+      <c r="B326" s="1"/>
+      <c r="D326" s="15" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="327" ht="14.25">
+      <c r="B327" s="1"/>
+      <c r="D327" s="15" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="328" ht="14.25">
+      <c r="B328" s="1"/>
+      <c r="D328" s="15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="329" ht="14.25">
+      <c r="B329" s="1"/>
+      <c r="D329" s="15" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="330" ht="14.25">
+      <c r="B330" s="1"/>
+      <c r="D330" s="15" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="331" ht="14.25">
+      <c r="B331" s="1"/>
+      <c r="D331" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="332" ht="14.25">
+      <c r="B332" s="1"/>
+      <c r="D332" s="15" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="333" ht="14.25">
+      <c r="B333" s="1"/>
+      <c r="D333" s="15" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="334" ht="14.25">
+      <c r="B334" s="1"/>
+      <c r="D334" s="15" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="335" ht="14.25">
+      <c r="B335" s="1"/>
+      <c r="D335" s="15" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="336" ht="14.25">
+      <c r="B336" s="1"/>
+      <c r="D336" s="15" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="337" ht="14.25">
+      <c r="B337" s="1"/>
+      <c r="D337" s="15" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="338" ht="14.25">
+      <c r="B338" s="1"/>
+      <c r="D338" s="15" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="339" ht="14.25">
+      <c r="B339" s="1"/>
+      <c r="D339" s="15" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="340" ht="14.25">
+      <c r="B340" s="1"/>
+      <c r="D340" s="15" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="341" ht="14.25">
+      <c r="B341" s="1"/>
+      <c r="D341" s="15" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="342" ht="14.25">
+      <c r="B342" s="1"/>
+      <c r="D342" s="15" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="343" ht="14.25">
+      <c r="B343" s="1"/>
+      <c r="D343" s="15" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="344" ht="14.25">
+      <c r="B344" s="1"/>
+      <c r="D344" s="15" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="345" ht="14.25">
+      <c r="B345" s="1"/>
+      <c r="D345" s="15" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="346" ht="14.25">
+      <c r="B346" s="1"/>
+      <c r="D346" s="15" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="347" ht="14.25">
+      <c r="B347" s="1"/>
+      <c r="D347" s="15" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="348" ht="14.25">
+      <c r="B348" s="1"/>
+      <c r="D348" s="15" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="349" ht="14.25">
+      <c r="B349" s="1"/>
+      <c r="D349" s="15" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="350" ht="14.25">
+      <c r="B350" s="1"/>
+      <c r="D350" s="15" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="351" ht="14.25">
+      <c r="B351" s="1"/>
+      <c r="D351" s="15" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="352" ht="14.25">
+      <c r="B352" s="1"/>
+      <c r="D352" s="15" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="353" ht="14.25">
+      <c r="B353" s="1"/>
+      <c r="D353" s="15" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="354" ht="14.25">
+      <c r="B354" s="1"/>
+      <c r="D354" s="15" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="355" ht="14.25">
+      <c r="B355" s="1"/>
+      <c r="D355" s="15" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="356" ht="14.25">
+      <c r="B356" s="1"/>
+      <c r="D356" s="15" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="357" ht="14.25">
+      <c r="B357" s="1"/>
+      <c r="D357" s="15" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="358" ht="14.25">
+      <c r="B358" s="1"/>
+      <c r="D358" s="15" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="359" ht="14.25">
+      <c r="B359" s="1"/>
+      <c r="D359" s="15" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="360" ht="14.25">
+      <c r="B360" s="1"/>
+      <c r="D360" s="15" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="361" ht="14.25">
+      <c r="B361" s="1"/>
+      <c r="D361" s="15" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="362" ht="14.25">
+      <c r="B362" s="1"/>
+      <c r="D362" s="15" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="363" ht="14.25">
+      <c r="B363" s="1"/>
+      <c r="D363" s="15" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="364" ht="14.25">
+      <c r="B364" s="1"/>
+      <c r="D364" s="15" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="365" ht="14.25">
+      <c r="B365" s="1"/>
+      <c r="D365" s="15" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="366" ht="14.25">
+      <c r="B366" s="1"/>
+      <c r="D366" s="15" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="367" ht="14.25">
+      <c r="B367" s="1"/>
+      <c r="D367" s="15" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="368" ht="14.25">
+      <c r="B368" s="1"/>
+      <c r="D368" s="15" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="369" ht="14.25">
+      <c r="B369" s="1"/>
+      <c r="D369" s="15" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="370" ht="14.25">
+      <c r="B370" s="1"/>
+      <c r="D370" s="15" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="371" ht="14.25">
+      <c r="B371" s="1"/>
+      <c r="D371" s="15" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="372" ht="14.25">
+      <c r="B372" s="1"/>
+      <c r="D372" s="15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="373" ht="14.25">
+      <c r="B373" s="1"/>
+      <c r="D373" s="15" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="374" ht="14.25">
+      <c r="B374" s="1"/>
+      <c r="D374" s="15" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="375" ht="14.25">
+      <c r="B375" s="1"/>
+      <c r="D375" s="15" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="376" ht="14.25">
+      <c r="B376" s="1"/>
+      <c r="D376" s="15" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="377" ht="14.25">
+      <c r="B377" s="1"/>
+      <c r="D377" s="15" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="378" ht="14.25">
+      <c r="B378" s="1"/>
+      <c r="D378" s="15" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="379" ht="14.25">
+      <c r="B379" s="1"/>
+      <c r="D379" s="15" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="380" ht="14.25">
+      <c r="B380" s="1"/>
+      <c r="D380" s="15" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="381" ht="14.25">
+      <c r="B381" s="1"/>
+      <c r="D381" s="15" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="382" ht="14.25">
+      <c r="B382" s="1"/>
+      <c r="D382" s="15" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="383" ht="14.25">
+      <c r="B383" s="1"/>
+      <c r="D383" s="15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="384" ht="14.25">
+      <c r="B384" s="1"/>
+      <c r="D384" s="15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="385" ht="14.25">
+      <c r="B385" s="1"/>
+      <c r="D385" s="15" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="386" ht="14.25">
+      <c r="B386" s="1"/>
+      <c r="D386" s="15" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="387" ht="14.25">
+      <c r="B387" s="1"/>
+      <c r="D387" s="15" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="388" ht="14.25">
+      <c r="B388" s="1"/>
+      <c r="D388" s="15" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="389" ht="14.25">
+      <c r="B389" s="1"/>
+      <c r="D389" s="15" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="390" ht="14.25">
+      <c r="B390" s="1"/>
+      <c r="D390" s="15" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="391" ht="14.25">
+      <c r="B391" s="1"/>
+      <c r="D391" s="15" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="392" ht="14.25">
+      <c r="B392" s="1"/>
+      <c r="D392" s="15" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="393" ht="14.25">
+      <c r="B393" s="1"/>
+      <c r="D393" s="15" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="394" ht="14.25">
+      <c r="B394" s="1"/>
+      <c r="D394" s="15" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="395" ht="14.25">
+      <c r="B395" s="1"/>
+      <c r="D395" s="15" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="396" ht="14.25">
+      <c r="B396" s="1"/>
+      <c r="D396" s="15" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="397" ht="14.25">
+      <c r="B397" s="1"/>
+      <c r="D397" s="15" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="398" ht="14.25">
+      <c r="B398" s="1"/>
+      <c r="D398" s="15" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="399" ht="14.25">
+      <c r="B399" s="1"/>
+      <c r="D399" s="15" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="400" ht="14.25">
+      <c r="B400" s="1"/>
+      <c r="D400" s="15" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="401" ht="14.25">
+      <c r="B401" s="1"/>
+      <c r="D401" s="15" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="402" ht="14.25">
+      <c r="B402" s="1"/>
+      <c r="D402" s="15" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="403" ht="14.25">
+      <c r="B403" s="1"/>
+      <c r="D403" s="15" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="404" ht="14.25">
+      <c r="B404" s="1"/>
+      <c r="D404" s="15" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="405" ht="14.25">
+      <c r="B405" s="1"/>
+      <c r="D405" s="15" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="406" ht="14.25">
+      <c r="B406" s="1"/>
+      <c r="D406" s="15" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="407" ht="14.25">
+      <c r="B407" s="1"/>
+      <c r="D407" s="15" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="408" ht="14.25">
+      <c r="B408" s="1"/>
+      <c r="D408" s="15" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="409" ht="14.25">
+      <c r="B409" s="1"/>
+      <c r="D409" s="15" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="410" ht="14.25">
+      <c r="B410" s="1"/>
+      <c r="D410" s="15" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="411" ht="14.25">
+      <c r="B411" s="1"/>
+      <c r="D411" s="15" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="412" ht="14.25">
+      <c r="B412" s="1"/>
+      <c r="D412" s="15" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="413" ht="14.25">
+      <c r="B413" s="1"/>
+      <c r="D413" s="15" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="414" ht="14.25">
+      <c r="B414" s="1"/>
+      <c r="D414" s="15" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="415" ht="14.25">
+      <c r="B415" s="1"/>
+      <c r="D415" s="15" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="416" ht="14.25">
+      <c r="B416" s="1"/>
+      <c r="D416" s="15" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="417" ht="14.25">
+      <c r="B417" s="1"/>
+      <c r="D417" s="15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="418" ht="14.25">
+      <c r="B418" s="1"/>
+      <c r="D418" s="15" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="419" ht="14.25">
+      <c r="B419" s="1"/>
+      <c r="D419" s="15" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="420" ht="14.25">
+      <c r="B420" s="1"/>
+      <c r="D420" s="15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="421" ht="14.25">
+      <c r="B421" s="1"/>
+      <c r="D421" s="15" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="422" ht="14.25">
+      <c r="B422" s="1"/>
+      <c r="D422" s="15" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="423" ht="14.25">
+      <c r="B423" s="1"/>
+      <c r="D423" s="15" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="424" ht="14.25">
+      <c r="B424" s="1"/>
+      <c r="D424" s="15" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="425" ht="14.25">
+      <c r="B425" s="1"/>
+      <c r="D425" s="15" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="426" ht="14.25">
+      <c r="B426" s="1"/>
+      <c r="D426" s="15" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="427" ht="14.25">
+      <c r="B427" s="1"/>
+      <c r="D427" s="15" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="428" ht="14.25">
+      <c r="B428" s="1"/>
+      <c r="D428" s="15" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="429" ht="14.25">
+      <c r="B429" s="1"/>
+      <c r="D429" s="15" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="430" ht="14.25">
+      <c r="B430" s="1"/>
+      <c r="D430" s="15" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="431" ht="14.25">
+      <c r="B431" s="1"/>
+      <c r="D431" s="15" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="432" ht="14.25">
+      <c r="B432" s="1"/>
+      <c r="D432" s="15" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="433" ht="14.25">
+      <c r="D433" s="15" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="434" ht="14.25">
+      <c r="D434" s="15" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="435" ht="14.25">
+      <c r="D435" s="15" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="436" ht="14.25">
+      <c r="D436" s="15" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="437" ht="14.25">
+      <c r="D437" s="15" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="438" ht="14.25">
+      <c r="D438" s="15" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="439" ht="14.25">
+      <c r="D439" s="15" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="440" ht="14.25">
+      <c r="D440" s="15" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="441" ht="14.25">
+      <c r="D441" s="15" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="442" ht="14.25">
+      <c r="D442" s="15" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="443" ht="14.25">
+      <c r="D443" s="15" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="444" ht="14.25">
+      <c r="D444" s="15" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="445" ht="14.25">
+      <c r="D445" s="15" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="446" ht="14.25">
+      <c r="D446" s="15" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="447" ht="14.25">
+      <c r="D447" s="15" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="448" ht="14.25">
+      <c r="D448" s="15" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="449" ht="14.25">
+      <c r="D449" s="15" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="450" ht="14.25">
+      <c r="D450" s="15" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="451" ht="14.25">
+      <c r="D451" s="15" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="452" ht="14.25">
+      <c r="D452" s="15" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="453" ht="14.25">
+      <c r="D453" s="15" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="454" ht="14.25">
+      <c r="D454" s="15" t="s">
+        <v>440</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -2059,66 +7301,60 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1">
-      <c r="A1" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>96</v>
+      <c r="A1" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" s="5"/>
+      <c r="A2" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="D2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="5"/>
+      <c r="A3" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="D3" s="6"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="5"/>
+      <c r="A4" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/documents/cogna-process-progress-fields.xlsx
+++ b/documents/cogna-process-progress-fields.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="fields" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="options" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="attacheds" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="optionsAttacheds" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="658">
   <si>
     <t>label</t>
   </si>
@@ -1974,6 +1975,24 @@
   </si>
   <si>
     <t>CADASTRAR_JULGAMENTO</t>
+  </si>
+  <si>
+    <t>optionValue</t>
+  </si>
+  <si>
+    <t>attachedKeys</t>
+  </si>
+  <si>
+    <t>attachedValues</t>
+  </si>
+  <si>
+    <t>TIPO_ANDAMENTO</t>
+  </si>
+  <si>
+    <t>NUMERO_PROCESSO,OCORRENCIA</t>
+  </si>
+  <si>
+    <t>1111,2222;a,b,c</t>
   </si>
 </sst>
 </file>
@@ -2025,7 +2044,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2062,6 +2081,12 @@
         <bgColor theme="9" tint="0.39997558519241921"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor theme="5" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2092,7 +2117,7 @@
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2101,9 +2126,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2136,6 +2158,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="3" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2677,7 +2709,7 @@
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="4" t="b">
@@ -2687,14 +2719,14 @@
         <v>10</v>
       </c>
       <c r="E2" s="4"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6" t="b">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H2" s="4"/>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -2712,7 +2744,7 @@
       <c r="H3" s="4"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -2768,7 +2800,7 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2786,7 +2818,7 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -2826,7 +2858,7 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -2866,7 +2898,7 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2886,7 +2918,7 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -2984,7 +3016,7 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -3082,7 +3114,7 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -3100,7 +3132,7 @@
       <c r="H23" s="4"/>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -3118,7 +3150,7 @@
       <c r="H24" s="4"/>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -3136,7 +3168,7 @@
       <c r="H25" s="4"/>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -3154,7 +3186,7 @@
       <c r="H26" s="4"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -3172,7 +3204,7 @@
       <c r="H27" s="4"/>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -3263,14 +3295,14 @@
       <c r="E32" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6" t="b">
+      <c r="F32" s="5"/>
+      <c r="G32" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="4"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -3281,14 +3313,14 @@
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="6"/>
+      <c r="F33" s="5"/>
       <c r="G33" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>43</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -3299,14 +3331,14 @@
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="6"/>
+      <c r="F34" s="5"/>
       <c r="G34" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -3317,7 +3349,7 @@
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="6"/>
+      <c r="F35" s="5"/>
       <c r="G35" s="4" t="b">
         <v>1</v>
       </c>
@@ -3329,7 +3361,7 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="9"/>
+      <c r="F36" s="8"/>
       <c r="H36" s="1"/>
     </row>
   </sheetData>
@@ -3355,19 +3387,19 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3375,16 +3407,16 @@
       <c r="A2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="13" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3392,16 +3424,16 @@
       <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3409,16 +3441,16 @@
       <c r="A4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3426,16 +3458,16 @@
       <c r="A5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3443,76 +3475,76 @@
       <c r="A6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="12"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="12"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="12"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="12"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
@@ -3521,103 +3553,103 @@
       <c r="B11" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="12"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="12"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="12"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="12"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="12"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="12"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="12"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
@@ -3626,43 +3658,43 @@
       <c r="B18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="12"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="12"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
@@ -3671,73 +3703,73 @@
       <c r="B21" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="E21" s="12"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E22" s="12"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E23" s="12"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="12"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="12"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
@@ -3746,43 +3778,43 @@
       <c r="B26" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E26" s="12"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="12"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E28" s="12"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
@@ -3791,118 +3823,118 @@
       <c r="B29" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="12"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="E30" s="12"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="E31" s="12"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E32" s="12"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="E33" s="12"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="E34" s="12"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="E35" s="12"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="E36" s="12"/>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="4" t="s">
@@ -3911,103 +3943,103 @@
       <c r="B37" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="E37" s="12"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="E38" s="12"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="E39" s="12"/>
+      <c r="E39" s="11"/>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="E40" s="12"/>
+      <c r="E40" s="11"/>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E41" s="12"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E42" s="12"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E43" s="12"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" ht="14.25">
       <c r="A44" s="4" t="s">
@@ -4016,281 +4048,281 @@
       <c r="B44" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E44" s="12"/>
+      <c r="E44" s="11"/>
     </row>
     <row r="45" ht="14.25">
       <c r="A45" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E45" s="12"/>
+      <c r="E45" s="11"/>
     </row>
     <row r="46" ht="14.25">
       <c r="A46" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="E46" s="12"/>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="12"/>
+      <c r="E47" s="11"/>
     </row>
     <row r="48" ht="14.25">
       <c r="A48" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E48" s="12"/>
+      <c r="E48" s="11"/>
     </row>
     <row r="49" ht="14.25">
       <c r="A49" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="10" t="s">
         <v>220</v>
       </c>
       <c r="C49" s="4"/>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="E49" s="6"/>
+      <c r="E49" s="5"/>
     </row>
     <row r="50" ht="14.25">
       <c r="A50" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="10" t="s">
         <v>223</v>
       </c>
       <c r="C50" s="4"/>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="E50" s="6"/>
+      <c r="E50" s="5"/>
     </row>
     <row r="51" ht="14.25">
       <c r="A51" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="10" t="s">
         <v>225</v>
       </c>
       <c r="C51" s="4"/>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="E51" s="6"/>
+      <c r="E51" s="5"/>
     </row>
     <row r="52" ht="14.25">
       <c r="A52" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="10" t="s">
         <v>227</v>
       </c>
       <c r="C52" s="4"/>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="E52" s="6"/>
+      <c r="E52" s="5"/>
     </row>
     <row r="53" ht="14.25">
       <c r="A53" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="10" t="s">
         <v>230</v>
       </c>
       <c r="C53" s="4"/>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="E53" s="6"/>
+      <c r="E53" s="5"/>
     </row>
     <row r="54" ht="14.25">
       <c r="A54" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="10" t="s">
         <v>233</v>
       </c>
       <c r="C54" s="4"/>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="E54" s="6"/>
+      <c r="E54" s="5"/>
     </row>
     <row r="55" ht="14.25">
       <c r="A55" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="10" t="s">
         <v>236</v>
       </c>
       <c r="C55" s="4"/>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="E55" s="6"/>
+      <c r="E55" s="5"/>
     </row>
     <row r="56" ht="14.25">
       <c r="A56" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="10" t="s">
         <v>239</v>
       </c>
       <c r="C56" s="4"/>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="E56" s="6"/>
+      <c r="E56" s="5"/>
     </row>
     <row r="57" ht="14.25">
       <c r="A57" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="10" t="s">
         <v>242</v>
       </c>
       <c r="C57" s="4"/>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E57" s="6"/>
+      <c r="E57" s="5"/>
     </row>
     <row r="58" ht="14.25">
       <c r="A58" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="10" t="s">
         <v>244</v>
       </c>
       <c r="C58" s="4"/>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="E58" s="6"/>
+      <c r="E58" s="5"/>
     </row>
     <row r="59" ht="14.25">
       <c r="A59" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C59" s="4"/>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E59" s="6"/>
+      <c r="E59" s="5"/>
     </row>
     <row r="60" ht="14.25">
       <c r="A60" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="10" t="s">
         <v>248</v>
       </c>
       <c r="C60" s="4"/>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="E60" s="6"/>
+      <c r="E60" s="5"/>
     </row>
     <row r="61" ht="14.25">
       <c r="A61" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="10" t="s">
         <v>250</v>
       </c>
       <c r="C61" s="4"/>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E61" s="6"/>
+      <c r="E61" s="5"/>
     </row>
     <row r="62" ht="14.25">
       <c r="A62" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="10" t="s">
         <v>252</v>
       </c>
       <c r="C62" s="4"/>
-      <c r="D62" s="13" t="s">
+      <c r="D62" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E62" s="6"/>
+      <c r="E62" s="5"/>
     </row>
     <row r="63" ht="14.25">
       <c r="A63" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="10" t="s">
         <v>254</v>
       </c>
       <c r="C63" s="4"/>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E63" s="6"/>
+      <c r="E63" s="5"/>
     </row>
     <row r="64" ht="14.25">
       <c r="A64" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="10" t="s">
         <v>256</v>
       </c>
       <c r="C64" s="4"/>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E64" s="6"/>
+      <c r="E64" s="5"/>
     </row>
     <row r="65" ht="14.25">
       <c r="A65" s="4" t="s">
@@ -4300,218 +4332,218 @@
         <v>258</v>
       </c>
       <c r="C65" s="4"/>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E65" s="6"/>
+      <c r="E65" s="5"/>
     </row>
     <row r="66" ht="14.25">
       <c r="A66" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="10" t="s">
         <v>260</v>
       </c>
       <c r="C66" s="4"/>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E66" s="6"/>
+      <c r="E66" s="5"/>
     </row>
     <row r="67" ht="14.25">
       <c r="A67" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="10" t="s">
         <v>262</v>
       </c>
       <c r="C67" s="4"/>
-      <c r="D67" s="13" t="s">
+      <c r="D67" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="E67" s="6"/>
+      <c r="E67" s="5"/>
     </row>
     <row r="68" ht="14.25">
       <c r="A68" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="10" t="s">
         <v>264</v>
       </c>
       <c r="C68" s="4"/>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="E68" s="6"/>
+      <c r="E68" s="5"/>
     </row>
     <row r="69" ht="14.25">
       <c r="A69" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="10" t="s">
         <v>265</v>
       </c>
       <c r="C69" s="4"/>
-      <c r="D69" s="13" t="s">
+      <c r="D69" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="E69" s="6"/>
+      <c r="E69" s="5"/>
     </row>
     <row r="70" ht="14.25">
       <c r="A70" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="10" t="s">
         <v>267</v>
       </c>
       <c r="C70" s="4"/>
-      <c r="D70" s="13" t="s">
+      <c r="D70" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E70" s="6"/>
+      <c r="E70" s="5"/>
     </row>
     <row r="71" ht="14.25">
       <c r="A71" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="10" t="s">
         <v>269</v>
       </c>
       <c r="C71" s="4"/>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E71" s="6"/>
+      <c r="E71" s="5"/>
     </row>
     <row r="72" ht="14.25">
       <c r="A72" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="10" t="s">
         <v>271</v>
       </c>
       <c r="C72" s="4"/>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="E72" s="6"/>
+      <c r="E72" s="5"/>
     </row>
     <row r="73" ht="14.25">
       <c r="A73" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="10" t="s">
         <v>273</v>
       </c>
       <c r="C73" s="4"/>
-      <c r="D73" s="13" t="s">
+      <c r="D73" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="E73" s="6"/>
+      <c r="E73" s="5"/>
     </row>
     <row r="74" ht="14.25">
       <c r="A74" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="10" t="s">
         <v>275</v>
       </c>
       <c r="C74" s="4"/>
-      <c r="D74" s="13" t="s">
+      <c r="D74" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="E74" s="6"/>
+      <c r="E74" s="5"/>
     </row>
     <row r="75" ht="14.25">
       <c r="A75" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="10" t="s">
         <v>277</v>
       </c>
       <c r="C75" s="4"/>
-      <c r="D75" s="13" t="s">
+      <c r="D75" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="E75" s="6"/>
+      <c r="E75" s="5"/>
     </row>
     <row r="76" ht="14.25">
       <c r="A76" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="10" t="s">
         <v>279</v>
       </c>
       <c r="C76" s="4"/>
-      <c r="D76" s="13" t="s">
+      <c r="D76" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="E76" s="6"/>
+      <c r="E76" s="5"/>
     </row>
     <row r="77" ht="14.25">
       <c r="A77" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="10" t="s">
         <v>281</v>
       </c>
       <c r="C77" s="4"/>
-      <c r="D77" s="13" t="s">
+      <c r="D77" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E77" s="6"/>
+      <c r="E77" s="5"/>
     </row>
     <row r="78" ht="14.25">
       <c r="A78" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="10" t="s">
         <v>283</v>
       </c>
       <c r="C78" s="4"/>
-      <c r="D78" s="13" t="s">
+      <c r="D78" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="E78" s="6"/>
+      <c r="E78" s="5"/>
     </row>
     <row r="79" ht="14.25">
       <c r="A79" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="10" t="s">
         <v>285</v>
       </c>
       <c r="C79" s="4"/>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="E79" s="6"/>
+      <c r="E79" s="5"/>
     </row>
     <row r="80" ht="14.25">
       <c r="A80" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="10" t="s">
         <v>287</v>
       </c>
       <c r="C80" s="4"/>
-      <c r="D80" s="13" t="s">
+      <c r="D80" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="E80" s="6"/>
+      <c r="E80" s="5"/>
     </row>
     <row r="81" ht="14.25">
       <c r="A81" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="10" t="s">
         <v>289</v>
       </c>
       <c r="C81" s="4"/>
-      <c r="D81" s="13" t="s">
+      <c r="D81" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="E81" s="6"/>
+      <c r="E81" s="5"/>
     </row>
     <row r="82" ht="14.25">
       <c r="A82" s="4" t="s">
@@ -4521,36 +4553,36 @@
         <v>291</v>
       </c>
       <c r="C82" s="4"/>
-      <c r="D82" s="13" t="s">
+      <c r="D82" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="E82" s="6"/>
+      <c r="E82" s="5"/>
     </row>
     <row r="83" ht="14.25">
       <c r="A83" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="10" t="s">
         <v>293</v>
       </c>
       <c r="C83" s="4"/>
-      <c r="D83" s="13" t="s">
+      <c r="D83" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="E83" s="6"/>
+      <c r="E83" s="5"/>
     </row>
     <row r="84" ht="14.25">
       <c r="A84" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="10" t="s">
         <v>295</v>
       </c>
       <c r="C84" s="4"/>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="E84" s="6"/>
+      <c r="E84" s="5"/>
     </row>
     <row r="85" ht="14.25">
       <c r="A85" s="4" t="s">
@@ -4560,140 +4592,140 @@
         <v>296</v>
       </c>
       <c r="C85" s="4"/>
-      <c r="D85" s="13" t="s">
+      <c r="D85" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="E85" s="6"/>
+      <c r="E85" s="5"/>
     </row>
     <row r="86" ht="14.25">
       <c r="A86" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="10" t="s">
         <v>298</v>
       </c>
       <c r="C86" s="4"/>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="E86" s="6"/>
+      <c r="E86" s="5"/>
     </row>
     <row r="87" ht="14.25">
       <c r="A87" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="10" t="s">
         <v>300</v>
       </c>
       <c r="C87" s="4"/>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="E87" s="6"/>
+      <c r="E87" s="5"/>
     </row>
     <row r="88" ht="14.25">
       <c r="A88" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="10" t="s">
         <v>301</v>
       </c>
       <c r="C88" s="4"/>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="E88" s="6"/>
+      <c r="E88" s="5"/>
     </row>
     <row r="89" ht="14.25">
       <c r="A89" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="10" t="s">
         <v>58</v>
       </c>
       <c r="C89" s="4"/>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="E89" s="6"/>
+      <c r="E89" s="5"/>
     </row>
     <row r="90" ht="14.25">
       <c r="A90" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="10" t="s">
         <v>302</v>
       </c>
       <c r="C90" s="4"/>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="E90" s="6"/>
+      <c r="E90" s="5"/>
     </row>
     <row r="91" ht="14.25">
       <c r="A91" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="10" t="s">
         <v>303</v>
       </c>
       <c r="C91" s="4"/>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="E91" s="6"/>
+      <c r="E91" s="5"/>
     </row>
     <row r="92" ht="14.25">
       <c r="A92" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="10" t="s">
         <v>304</v>
       </c>
       <c r="C92" s="4"/>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="E92" s="6"/>
+      <c r="E92" s="5"/>
     </row>
     <row r="93" ht="14.25">
       <c r="A93" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="10" t="s">
         <v>306</v>
       </c>
       <c r="C93" s="4"/>
-      <c r="D93" s="13" t="s">
+      <c r="D93" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="E93" s="6"/>
+      <c r="E93" s="5"/>
     </row>
     <row r="94" ht="14.25">
       <c r="A94" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="10" t="s">
         <v>308</v>
       </c>
       <c r="C94" s="4"/>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="E94" s="6"/>
+      <c r="E94" s="5"/>
     </row>
     <row r="95" ht="14.25">
       <c r="A95" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="10" t="s">
         <v>310</v>
       </c>
       <c r="C95" s="4"/>
-      <c r="D95" s="13" t="s">
+      <c r="D95" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="E95" s="6"/>
+      <c r="E95" s="5"/>
     </row>
     <row r="96" ht="14.25">
       <c r="A96" s="4" t="s">
@@ -4703,88 +4735,88 @@
         <v>312</v>
       </c>
       <c r="C96" s="4"/>
-      <c r="D96" s="13" t="s">
+      <c r="D96" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="E96" s="6"/>
+      <c r="E96" s="5"/>
     </row>
     <row r="97" ht="14.25">
       <c r="A97" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="10" t="s">
         <v>315</v>
       </c>
       <c r="C97" s="4"/>
-      <c r="D97" s="13" t="s">
+      <c r="D97" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="E97" s="6"/>
+      <c r="E97" s="5"/>
     </row>
     <row r="98" ht="14.25">
       <c r="A98" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="10" t="s">
         <v>318</v>
       </c>
       <c r="C98" s="4"/>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="E98" s="6"/>
+      <c r="E98" s="5"/>
     </row>
     <row r="99" ht="14.25">
       <c r="A99" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="10" t="s">
         <v>321</v>
       </c>
       <c r="C99" s="4"/>
-      <c r="D99" s="13" t="s">
+      <c r="D99" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="E99" s="6"/>
+      <c r="E99" s="5"/>
     </row>
     <row r="100" ht="14.25">
       <c r="A100" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="10" t="s">
         <v>324</v>
       </c>
       <c r="C100" s="4"/>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="E100" s="6"/>
+      <c r="E100" s="5"/>
     </row>
     <row r="101" ht="14.25">
       <c r="A101" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="10" t="s">
         <v>327</v>
       </c>
       <c r="C101" s="4"/>
-      <c r="D101" s="13" t="s">
+      <c r="D101" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="E101" s="6"/>
+      <c r="E101" s="5"/>
     </row>
     <row r="102" ht="14.25">
       <c r="A102" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="10" t="s">
         <v>330</v>
       </c>
       <c r="C102" s="4"/>
-      <c r="D102" s="13" t="s">
+      <c r="D102" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E102" s="6"/>
+      <c r="E102" s="5"/>
     </row>
     <row r="103" ht="14.25">
       <c r="A103" s="4" t="s">
@@ -4794,36 +4826,36 @@
         <v>333</v>
       </c>
       <c r="C103" s="4"/>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="E103" s="6"/>
+      <c r="E103" s="5"/>
     </row>
     <row r="104" ht="14.25">
       <c r="A104" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="10" t="s">
         <v>336</v>
       </c>
       <c r="C104" s="4"/>
-      <c r="D104" s="13" t="s">
+      <c r="D104" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="E104" s="6"/>
+      <c r="E104" s="5"/>
     </row>
     <row r="105" ht="14.25">
       <c r="A105" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="10" t="s">
         <v>339</v>
       </c>
       <c r="C105" s="4"/>
-      <c r="D105" s="13" t="s">
+      <c r="D105" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="E105" s="6"/>
+      <c r="E105" s="5"/>
     </row>
     <row r="106" ht="14.25">
       <c r="A106" s="4" t="s">
@@ -4833,89 +4865,89 @@
         <v>342</v>
       </c>
       <c r="C106" s="4"/>
-      <c r="D106" s="13" t="s">
+      <c r="D106" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="E106" s="6"/>
+      <c r="E106" s="5"/>
     </row>
     <row r="107" ht="14.25">
       <c r="A107" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="10" t="s">
         <v>345</v>
       </c>
       <c r="C107" s="4"/>
-      <c r="D107" s="13" t="s">
+      <c r="D107" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="E107" s="6"/>
+      <c r="E107" s="5"/>
     </row>
     <row r="108" ht="14.25">
       <c r="A108" s="4"/>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="10" t="s">
         <v>347</v>
       </c>
       <c r="C108" s="4"/>
-      <c r="D108" s="13" t="s">
+      <c r="D108" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="E108" s="6"/>
+      <c r="E108" s="5"/>
     </row>
     <row r="109" ht="14.25">
       <c r="A109" s="4"/>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="10" t="s">
         <v>349</v>
       </c>
       <c r="C109" s="4"/>
-      <c r="D109" s="13" t="s">
+      <c r="D109" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="E109" s="6"/>
+      <c r="E109" s="5"/>
     </row>
     <row r="110" ht="14.25">
       <c r="A110" s="4"/>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="10" t="s">
         <v>351</v>
       </c>
       <c r="C110" s="4"/>
-      <c r="D110" s="13" t="s">
+      <c r="D110" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="E110" s="6"/>
+      <c r="E110" s="5"/>
     </row>
     <row r="111" ht="14.25">
       <c r="A111" s="4"/>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="10" t="s">
         <v>353</v>
       </c>
       <c r="C111" s="4"/>
-      <c r="D111" s="13" t="s">
+      <c r="D111" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="E111" s="6"/>
+      <c r="E111" s="5"/>
     </row>
     <row r="112" ht="14.25">
       <c r="A112" s="4"/>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="10" t="s">
         <v>355</v>
       </c>
       <c r="C112" s="4"/>
-      <c r="D112" s="13" t="s">
+      <c r="D112" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="E112" s="6"/>
+      <c r="E112" s="5"/>
     </row>
     <row r="113" ht="14.25">
       <c r="A113" s="4"/>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="10" t="s">
         <v>259</v>
       </c>
       <c r="C113" s="4"/>
-      <c r="D113" s="13" t="s">
+      <c r="D113" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="E113" s="6"/>
+      <c r="E113" s="5"/>
     </row>
     <row r="114" ht="14.25">
       <c r="A114" s="4"/>
@@ -4923,76 +4955,76 @@
         <v>358</v>
       </c>
       <c r="C114" s="4"/>
-      <c r="D114" s="13" t="s">
+      <c r="D114" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="E114" s="6"/>
+      <c r="E114" s="5"/>
     </row>
     <row r="115" ht="14.25">
       <c r="A115" s="4"/>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="10" t="s">
         <v>360</v>
       </c>
       <c r="C115" s="4"/>
-      <c r="D115" s="13" t="s">
+      <c r="D115" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="E115" s="6"/>
+      <c r="E115" s="5"/>
     </row>
     <row r="116" ht="14.25">
       <c r="A116" s="4"/>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="10" t="s">
         <v>272</v>
       </c>
       <c r="C116" s="4"/>
-      <c r="D116" s="13" t="s">
+      <c r="D116" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="E116" s="6"/>
+      <c r="E116" s="5"/>
     </row>
     <row r="117" ht="14.25">
       <c r="A117" s="4"/>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="10" t="s">
         <v>363</v>
       </c>
       <c r="C117" s="4"/>
-      <c r="D117" s="13" t="s">
+      <c r="D117" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="E117" s="6"/>
+      <c r="E117" s="5"/>
     </row>
     <row r="118" ht="14.25">
       <c r="A118" s="4"/>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="10" t="s">
         <v>365</v>
       </c>
       <c r="C118" s="4"/>
-      <c r="D118" s="13" t="s">
+      <c r="D118" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="E118" s="6"/>
+      <c r="E118" s="5"/>
     </row>
     <row r="119" ht="14.25">
       <c r="A119" s="4"/>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="10" t="s">
         <v>367</v>
       </c>
       <c r="C119" s="4"/>
-      <c r="D119" s="13" t="s">
+      <c r="D119" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="E119" s="6"/>
+      <c r="E119" s="5"/>
     </row>
     <row r="120" ht="14.25">
       <c r="A120" s="4"/>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="10" t="s">
         <v>369</v>
       </c>
       <c r="C120" s="4"/>
-      <c r="D120" s="13" t="s">
+      <c r="D120" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="E120" s="6"/>
+      <c r="E120" s="5"/>
     </row>
     <row r="121" ht="14.25">
       <c r="A121" s="4"/>
@@ -5000,43 +5032,43 @@
         <v>371</v>
       </c>
       <c r="C121" s="4"/>
-      <c r="D121" s="13" t="s">
+      <c r="D121" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="E121" s="6"/>
+      <c r="E121" s="5"/>
     </row>
     <row r="122" ht="14.25">
       <c r="A122" s="4"/>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="10" t="s">
         <v>373</v>
       </c>
       <c r="C122" s="4"/>
-      <c r="D122" s="13" t="s">
+      <c r="D122" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="E122" s="6"/>
+      <c r="E122" s="5"/>
     </row>
     <row r="123" ht="14.25">
       <c r="A123" s="4"/>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="10" t="s">
         <v>375</v>
       </c>
       <c r="C123" s="4"/>
-      <c r="D123" s="13" t="s">
+      <c r="D123" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="E123" s="6"/>
+      <c r="E123" s="5"/>
     </row>
     <row r="124" ht="14.25">
       <c r="A124" s="4"/>
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="10" t="s">
         <v>377</v>
       </c>
       <c r="C124" s="4"/>
-      <c r="D124" s="13" t="s">
+      <c r="D124" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="E124" s="6"/>
+      <c r="E124" s="5"/>
     </row>
     <row r="125" ht="14.25">
       <c r="A125" s="4"/>
@@ -5044,54 +5076,54 @@
         <v>379</v>
       </c>
       <c r="C125" s="4"/>
-      <c r="D125" s="13" t="s">
+      <c r="D125" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="E125" s="6"/>
+      <c r="E125" s="5"/>
     </row>
     <row r="126" ht="14.25">
       <c r="A126" s="4"/>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="10" t="s">
         <v>381</v>
       </c>
       <c r="C126" s="4"/>
-      <c r="D126" s="13" t="s">
+      <c r="D126" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="E126" s="6"/>
+      <c r="E126" s="5"/>
     </row>
     <row r="127" ht="14.25">
       <c r="A127" s="4"/>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="10" t="s">
         <v>383</v>
       </c>
       <c r="C127" s="4"/>
-      <c r="D127" s="13" t="s">
+      <c r="D127" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="E127" s="6"/>
+      <c r="E127" s="5"/>
     </row>
     <row r="128" ht="14.25">
       <c r="A128" s="4"/>
-      <c r="B128" s="11" t="s">
+      <c r="B128" s="10" t="s">
         <v>385</v>
       </c>
       <c r="C128" s="4"/>
-      <c r="D128" s="13" t="s">
+      <c r="D128" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="E128" s="6"/>
+      <c r="E128" s="5"/>
     </row>
     <row r="129" ht="14.25">
       <c r="A129" s="4"/>
-      <c r="B129" s="11" t="s">
+      <c r="B129" s="10" t="s">
         <v>387</v>
       </c>
       <c r="C129" s="4"/>
-      <c r="D129" s="13" t="s">
+      <c r="D129" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="E129" s="6"/>
+      <c r="E129" s="5"/>
     </row>
     <row r="130" ht="14.25">
       <c r="A130" s="4"/>
@@ -5099,131 +5131,131 @@
         <v>389</v>
       </c>
       <c r="C130" s="4"/>
-      <c r="D130" s="13" t="s">
+      <c r="D130" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="E130" s="6"/>
+      <c r="E130" s="5"/>
     </row>
     <row r="131" ht="14.25">
       <c r="A131" s="4"/>
-      <c r="B131" s="11" t="s">
+      <c r="B131" s="10" t="s">
         <v>391</v>
       </c>
       <c r="C131" s="4"/>
-      <c r="D131" s="13" t="s">
+      <c r="D131" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="E131" s="6"/>
+      <c r="E131" s="5"/>
     </row>
     <row r="132" ht="14.25">
       <c r="A132" s="4"/>
-      <c r="B132" s="11" t="s">
+      <c r="B132" s="10" t="s">
         <v>393</v>
       </c>
       <c r="C132" s="4"/>
-      <c r="D132" s="13" t="s">
+      <c r="D132" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="E132" s="6"/>
+      <c r="E132" s="5"/>
     </row>
     <row r="133" ht="14.25">
       <c r="A133" s="4"/>
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="10" t="s">
         <v>395</v>
       </c>
       <c r="C133" s="4"/>
-      <c r="D133" s="13" t="s">
+      <c r="D133" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E133" s="6"/>
+      <c r="E133" s="5"/>
     </row>
     <row r="134" ht="14.25">
       <c r="A134" s="4"/>
-      <c r="B134" s="11" t="s">
+      <c r="B134" s="10" t="s">
         <v>397</v>
       </c>
       <c r="C134" s="4"/>
-      <c r="D134" s="13" t="s">
+      <c r="D134" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="E134" s="6"/>
+      <c r="E134" s="5"/>
     </row>
     <row r="135" ht="14.25">
       <c r="A135" s="4"/>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="10" t="s">
         <v>398</v>
       </c>
       <c r="C135" s="4"/>
-      <c r="D135" s="13" t="s">
+      <c r="D135" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="E135" s="6"/>
+      <c r="E135" s="5"/>
     </row>
     <row r="136" ht="14.25">
       <c r="A136" s="4"/>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="10" t="s">
         <v>400</v>
       </c>
       <c r="C136" s="4"/>
-      <c r="D136" s="13" t="s">
+      <c r="D136" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="E136" s="6"/>
+      <c r="E136" s="5"/>
     </row>
     <row r="137" ht="14.25">
       <c r="A137" s="4"/>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="10" t="s">
         <v>402</v>
       </c>
       <c r="C137" s="4"/>
-      <c r="D137" s="13" t="s">
+      <c r="D137" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="E137" s="6"/>
+      <c r="E137" s="5"/>
     </row>
     <row r="138" ht="14.25">
       <c r="A138" s="4"/>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="10" t="s">
         <v>404</v>
       </c>
       <c r="C138" s="4"/>
-      <c r="D138" s="13" t="s">
+      <c r="D138" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="E138" s="6"/>
+      <c r="E138" s="5"/>
     </row>
     <row r="139" ht="14.25">
       <c r="A139" s="4"/>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="10" t="s">
         <v>406</v>
       </c>
       <c r="C139" s="4"/>
-      <c r="D139" s="13" t="s">
+      <c r="D139" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E139" s="6"/>
+      <c r="E139" s="5"/>
     </row>
     <row r="140" ht="14.25">
       <c r="A140" s="4"/>
-      <c r="B140" s="11" t="s">
+      <c r="B140" s="10" t="s">
         <v>407</v>
       </c>
       <c r="C140" s="4"/>
-      <c r="D140" s="13" t="s">
+      <c r="D140" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="E140" s="6"/>
+      <c r="E140" s="5"/>
     </row>
     <row r="141" ht="14.25">
       <c r="A141" s="4"/>
-      <c r="B141" s="11" t="s">
+      <c r="B141" s="10" t="s">
         <v>408</v>
       </c>
       <c r="C141" s="4"/>
-      <c r="D141" s="13" t="s">
+      <c r="D141" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="E141" s="6"/>
+      <c r="E141" s="5"/>
     </row>
     <row r="142" ht="14.25">
       <c r="A142" s="4"/>
@@ -5231,43 +5263,43 @@
         <v>409</v>
       </c>
       <c r="C142" s="4"/>
-      <c r="D142" s="13" t="s">
+      <c r="D142" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E142" s="6"/>
+      <c r="E142" s="5"/>
     </row>
     <row r="143" ht="14.25">
       <c r="A143" s="4"/>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="10" t="s">
         <v>410</v>
       </c>
       <c r="C143" s="4"/>
-      <c r="D143" s="13" t="s">
+      <c r="D143" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="E143" s="6"/>
+      <c r="E143" s="5"/>
     </row>
     <row r="144" ht="14.25">
       <c r="A144" s="4"/>
-      <c r="B144" s="11" t="s">
+      <c r="B144" s="10" t="s">
         <v>411</v>
       </c>
       <c r="C144" s="4"/>
-      <c r="D144" s="13" t="s">
+      <c r="D144" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="E144" s="6"/>
+      <c r="E144" s="5"/>
     </row>
     <row r="145" ht="14.25">
       <c r="A145" s="4"/>
-      <c r="B145" s="11" t="s">
+      <c r="B145" s="10" t="s">
         <v>412</v>
       </c>
       <c r="C145" s="4"/>
-      <c r="D145" s="13" t="s">
+      <c r="D145" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="E145" s="6"/>
+      <c r="E145" s="5"/>
     </row>
     <row r="146" ht="14.25">
       <c r="A146" s="4"/>
@@ -5275,76 +5307,76 @@
         <v>413</v>
       </c>
       <c r="C146" s="4"/>
-      <c r="D146" s="13" t="s">
+      <c r="D146" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="E146" s="6"/>
+      <c r="E146" s="5"/>
     </row>
     <row r="147" ht="14.25">
       <c r="A147" s="4"/>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="10" t="s">
         <v>414</v>
       </c>
       <c r="C147" s="4"/>
-      <c r="D147" s="13" t="s">
+      <c r="D147" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="E147" s="6"/>
+      <c r="E147" s="5"/>
     </row>
     <row r="148" ht="14.25">
       <c r="A148" s="4"/>
-      <c r="B148" s="11" t="s">
+      <c r="B148" s="10" t="s">
         <v>415</v>
       </c>
       <c r="C148" s="4"/>
-      <c r="D148" s="13" t="s">
+      <c r="D148" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="E148" s="6"/>
+      <c r="E148" s="5"/>
     </row>
     <row r="149" ht="14.25">
       <c r="A149" s="4"/>
-      <c r="B149" s="11" t="s">
+      <c r="B149" s="10" t="s">
         <v>416</v>
       </c>
       <c r="C149" s="4"/>
-      <c r="D149" s="13" t="s">
+      <c r="D149" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="E149" s="6"/>
+      <c r="E149" s="5"/>
     </row>
     <row r="150" ht="14.25">
       <c r="A150" s="4"/>
-      <c r="B150" s="11" t="s">
+      <c r="B150" s="10" t="s">
         <v>417</v>
       </c>
       <c r="C150" s="4"/>
-      <c r="D150" s="13" t="s">
+      <c r="D150" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="E150" s="6"/>
+      <c r="E150" s="5"/>
     </row>
     <row r="151" ht="14.25">
       <c r="A151" s="4"/>
-      <c r="B151" s="11" t="s">
+      <c r="B151" s="10" t="s">
         <v>418</v>
       </c>
       <c r="C151" s="4"/>
-      <c r="D151" s="13" t="s">
+      <c r="D151" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="E151" s="6"/>
+      <c r="E151" s="5"/>
     </row>
     <row r="152" ht="14.25">
       <c r="A152" s="4"/>
-      <c r="B152" s="11" t="s">
+      <c r="B152" s="10" t="s">
         <v>419</v>
       </c>
       <c r="C152" s="4"/>
-      <c r="D152" s="13" t="s">
+      <c r="D152" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="E152" s="6"/>
+      <c r="E152" s="5"/>
     </row>
     <row r="153" ht="14.25">
       <c r="A153" s="4"/>
@@ -5352,21 +5384,21 @@
         <v>420</v>
       </c>
       <c r="C153" s="4"/>
-      <c r="D153" s="13" t="s">
+      <c r="D153" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="E153" s="6"/>
+      <c r="E153" s="5"/>
     </row>
     <row r="154" ht="14.25">
       <c r="A154" s="4"/>
-      <c r="B154" s="11" t="s">
+      <c r="B154" s="10" t="s">
         <v>421</v>
       </c>
       <c r="C154" s="4"/>
-      <c r="D154" s="13" t="s">
+      <c r="D154" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="E154" s="6"/>
+      <c r="E154" s="5"/>
     </row>
     <row r="155" ht="14.25">
       <c r="A155" s="4"/>
@@ -5374,98 +5406,98 @@
         <v>422</v>
       </c>
       <c r="C155" s="4"/>
-      <c r="D155" s="13" t="s">
+      <c r="D155" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="E155" s="6"/>
+      <c r="E155" s="5"/>
     </row>
     <row r="156" ht="14.25">
       <c r="A156" s="4"/>
-      <c r="B156" s="11" t="s">
+      <c r="B156" s="10" t="s">
         <v>424</v>
       </c>
       <c r="C156" s="4"/>
-      <c r="D156" s="13" t="s">
+      <c r="D156" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="E156" s="6"/>
+      <c r="E156" s="5"/>
     </row>
     <row r="157" ht="14.25">
       <c r="A157" s="4"/>
-      <c r="B157" s="11" t="s">
+      <c r="B157" s="10" t="s">
         <v>425</v>
       </c>
       <c r="C157" s="4"/>
-      <c r="D157" s="13" t="s">
+      <c r="D157" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E157" s="6"/>
+      <c r="E157" s="5"/>
     </row>
     <row r="158" ht="14.25">
       <c r="A158" s="4"/>
-      <c r="B158" s="11" t="s">
+      <c r="B158" s="10" t="s">
         <v>426</v>
       </c>
       <c r="C158" s="4"/>
-      <c r="D158" s="13" t="s">
+      <c r="D158" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="E158" s="6"/>
+      <c r="E158" s="5"/>
     </row>
     <row r="159" ht="14.25">
       <c r="A159" s="4"/>
-      <c r="B159" s="11" t="s">
+      <c r="B159" s="10" t="s">
         <v>428</v>
       </c>
       <c r="C159" s="4"/>
-      <c r="D159" s="13" t="s">
+      <c r="D159" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="E159" s="6"/>
+      <c r="E159" s="5"/>
     </row>
     <row r="160" ht="14.25">
       <c r="A160" s="4"/>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="10" t="s">
         <v>430</v>
       </c>
       <c r="C160" s="4"/>
-      <c r="D160" s="13" t="s">
+      <c r="D160" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="E160" s="6"/>
+      <c r="E160" s="5"/>
     </row>
     <row r="161" ht="14.25">
       <c r="A161" s="4"/>
-      <c r="B161" s="11" t="s">
+      <c r="B161" s="10" t="s">
         <v>432</v>
       </c>
       <c r="C161" s="4"/>
-      <c r="D161" s="13" t="s">
+      <c r="D161" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="E161" s="6"/>
+      <c r="E161" s="5"/>
     </row>
     <row r="162" ht="14.25">
       <c r="A162" s="4"/>
-      <c r="B162" s="11" t="s">
+      <c r="B162" s="10" t="s">
         <v>434</v>
       </c>
       <c r="C162" s="4"/>
-      <c r="D162" s="13" t="s">
+      <c r="D162" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="E162" s="6"/>
+      <c r="E162" s="5"/>
     </row>
     <row r="163" ht="14.25">
       <c r="A163" s="4"/>
-      <c r="B163" s="11" t="s">
+      <c r="B163" s="10" t="s">
         <v>436</v>
       </c>
       <c r="C163" s="4"/>
-      <c r="D163" s="13" t="s">
+      <c r="D163" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="E163" s="6"/>
+      <c r="E163" s="5"/>
     </row>
     <row r="164" ht="14.25">
       <c r="A164" s="4"/>
@@ -5473,1812 +5505,1812 @@
         <v>438</v>
       </c>
       <c r="C164" s="4"/>
-      <c r="D164" s="13" t="s">
+      <c r="D164" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="E164" s="6"/>
+      <c r="E164" s="5"/>
     </row>
     <row r="165" ht="14.25">
       <c r="A165" s="4"/>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="10" t="s">
         <v>440</v>
       </c>
       <c r="C165" s="4"/>
-      <c r="D165" s="13" t="s">
+      <c r="D165" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="E165" s="6"/>
+      <c r="E165" s="5"/>
     </row>
     <row r="166" ht="14.25">
       <c r="A166" s="1"/>
-      <c r="B166" s="15"/>
+      <c r="B166" s="14"/>
       <c r="C166" s="1"/>
-      <c r="D166" s="15" t="s">
+      <c r="D166" s="14" t="s">
         <v>442</v>
       </c>
-      <c r="E166" s="9"/>
+      <c r="E166" s="8"/>
     </row>
     <row r="167" ht="14.25">
       <c r="A167" s="1"/>
-      <c r="B167" s="15"/>
+      <c r="B167" s="14"/>
       <c r="C167" s="1"/>
-      <c r="D167" s="15" t="s">
+      <c r="D167" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="E167" s="9"/>
+      <c r="E167" s="8"/>
     </row>
     <row r="168" ht="14.25">
       <c r="A168" s="1"/>
-      <c r="B168" s="15"/>
+      <c r="B168" s="14"/>
       <c r="C168" s="1"/>
-      <c r="D168" s="15" t="s">
+      <c r="D168" s="14" t="s">
         <v>444</v>
       </c>
-      <c r="E168" s="9"/>
+      <c r="E168" s="8"/>
     </row>
     <row r="169" ht="14.25">
       <c r="A169" s="1"/>
-      <c r="B169" s="15"/>
+      <c r="B169" s="14"/>
       <c r="C169" s="1"/>
-      <c r="D169" s="15" t="s">
+      <c r="D169" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="E169" s="9"/>
+      <c r="E169" s="8"/>
     </row>
     <row r="170" ht="14.25">
       <c r="A170" s="1"/>
-      <c r="B170" s="15"/>
+      <c r="B170" s="14"/>
       <c r="C170" s="1"/>
-      <c r="D170" s="15" t="s">
+      <c r="D170" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="E170" s="9"/>
+      <c r="E170" s="8"/>
     </row>
     <row r="171" ht="14.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
-      <c r="D171" s="15" t="s">
+      <c r="D171" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E171" s="9"/>
+      <c r="E171" s="8"/>
     </row>
     <row r="172" ht="14.25">
       <c r="A172" s="1"/>
-      <c r="B172" s="15"/>
+      <c r="B172" s="14"/>
       <c r="C172" s="1"/>
-      <c r="D172" s="15" t="s">
+      <c r="D172" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="E172" s="9"/>
+      <c r="E172" s="8"/>
     </row>
     <row r="173" ht="14.25">
       <c r="A173" s="1"/>
-      <c r="B173" s="15"/>
+      <c r="B173" s="14"/>
       <c r="C173" s="1"/>
-      <c r="D173" s="15" t="s">
+      <c r="D173" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="E173" s="9"/>
+      <c r="E173" s="8"/>
     </row>
     <row r="174" ht="14.25">
       <c r="A174" s="1"/>
-      <c r="B174" s="15"/>
+      <c r="B174" s="14"/>
       <c r="C174" s="1"/>
-      <c r="D174" s="15" t="s">
+      <c r="D174" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="E174" s="9"/>
+      <c r="E174" s="8"/>
     </row>
     <row r="175" ht="14.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
-      <c r="D175" s="15" t="s">
+      <c r="D175" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="E175" s="9"/>
+      <c r="E175" s="8"/>
     </row>
     <row r="176" ht="14.25">
       <c r="A176" s="1"/>
-      <c r="B176" s="15"/>
+      <c r="B176" s="14"/>
       <c r="C176" s="1"/>
-      <c r="D176" s="15" t="s">
+      <c r="D176" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="E176" s="9"/>
+      <c r="E176" s="8"/>
     </row>
     <row r="177" ht="14.25">
       <c r="A177" s="1"/>
-      <c r="B177" s="15"/>
+      <c r="B177" s="14"/>
       <c r="C177" s="1"/>
-      <c r="D177" s="15" t="s">
+      <c r="D177" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="E177" s="9"/>
+      <c r="E177" s="8"/>
     </row>
     <row r="178" ht="14.25">
       <c r="A178" s="1"/>
-      <c r="B178" s="15"/>
+      <c r="B178" s="14"/>
       <c r="C178" s="1"/>
-      <c r="D178" s="15" t="s">
+      <c r="D178" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="E178" s="9"/>
+      <c r="E178" s="8"/>
     </row>
     <row r="179" ht="14.25">
       <c r="A179" s="1"/>
-      <c r="B179" s="15"/>
+      <c r="B179" s="14"/>
       <c r="C179" s="1"/>
-      <c r="D179" s="15" t="s">
+      <c r="D179" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="E179" s="9"/>
+      <c r="E179" s="8"/>
     </row>
     <row r="180" ht="14.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
-      <c r="D180" s="15" t="s">
+      <c r="D180" s="14" t="s">
         <v>446</v>
       </c>
-      <c r="E180" s="9"/>
+      <c r="E180" s="8"/>
     </row>
     <row r="181" ht="14.25">
       <c r="A181" s="1"/>
-      <c r="B181" s="15"/>
+      <c r="B181" s="14"/>
       <c r="C181" s="1"/>
-      <c r="D181" s="15" t="s">
+      <c r="D181" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="E181" s="9"/>
+      <c r="E181" s="8"/>
     </row>
     <row r="182" ht="14.25">
       <c r="A182" s="1"/>
-      <c r="B182" s="15"/>
+      <c r="B182" s="14"/>
       <c r="C182" s="1"/>
-      <c r="D182" s="15" t="s">
+      <c r="D182" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="E182" s="9"/>
+      <c r="E182" s="8"/>
     </row>
     <row r="183" ht="14.25">
       <c r="A183" s="1"/>
-      <c r="B183" s="15"/>
+      <c r="B183" s="14"/>
       <c r="C183" s="1"/>
-      <c r="D183" s="15" t="s">
+      <c r="D183" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="E183" s="9"/>
+      <c r="E183" s="8"/>
     </row>
     <row r="184" ht="14.25">
       <c r="A184" s="1"/>
-      <c r="B184" s="15"/>
+      <c r="B184" s="14"/>
       <c r="C184" s="1"/>
-      <c r="D184" s="15" t="s">
+      <c r="D184" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="E184" s="9"/>
+      <c r="E184" s="8"/>
     </row>
     <row r="185" ht="14.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
-      <c r="D185" s="15" t="s">
+      <c r="D185" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="E185" s="9"/>
+      <c r="E185" s="8"/>
     </row>
     <row r="186" ht="14.25">
       <c r="A186" s="1"/>
-      <c r="B186" s="15"/>
+      <c r="B186" s="14"/>
       <c r="C186" s="1"/>
-      <c r="D186" s="15" t="s">
+      <c r="D186" s="14" t="s">
         <v>452</v>
       </c>
-      <c r="E186" s="9"/>
+      <c r="E186" s="8"/>
     </row>
     <row r="187" ht="14.25">
       <c r="A187" s="1"/>
-      <c r="B187" s="15"/>
+      <c r="B187" s="14"/>
       <c r="C187" s="1"/>
-      <c r="D187" s="15" t="s">
+      <c r="D187" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="E187" s="9"/>
+      <c r="E187" s="8"/>
     </row>
     <row r="188" ht="14.25">
       <c r="A188" s="1"/>
-      <c r="B188" s="15"/>
+      <c r="B188" s="14"/>
       <c r="C188" s="1"/>
-      <c r="D188" s="15" t="s">
+      <c r="D188" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="E188" s="9"/>
+      <c r="E188" s="8"/>
     </row>
     <row r="189" ht="14.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
-      <c r="D189" s="15" t="s">
+      <c r="D189" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="E189" s="9"/>
+      <c r="E189" s="8"/>
     </row>
     <row r="190" ht="14.25">
       <c r="A190" s="1"/>
-      <c r="B190" s="15"/>
+      <c r="B190" s="14"/>
       <c r="C190" s="1"/>
-      <c r="D190" s="15" t="s">
+      <c r="D190" s="14" t="s">
         <v>456</v>
       </c>
-      <c r="E190" s="9"/>
+      <c r="E190" s="8"/>
     </row>
     <row r="191" ht="14.25">
       <c r="A191" s="1"/>
-      <c r="B191" s="15"/>
+      <c r="B191" s="14"/>
       <c r="C191" s="1"/>
-      <c r="D191" s="15" t="s">
+      <c r="D191" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="E191" s="9"/>
+      <c r="E191" s="8"/>
     </row>
     <row r="192" ht="14.25">
       <c r="A192" s="1"/>
-      <c r="B192" s="15"/>
+      <c r="B192" s="14"/>
       <c r="C192" s="1"/>
-      <c r="D192" s="15" t="s">
+      <c r="D192" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="E192" s="9"/>
+      <c r="E192" s="8"/>
     </row>
     <row r="193" ht="14.25">
       <c r="B193" s="1"/>
-      <c r="D193" s="15" t="s">
+      <c r="D193" s="14" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="194" ht="14.25">
       <c r="B194" s="1"/>
-      <c r="D194" s="15" t="s">
+      <c r="D194" s="14" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="195" ht="14.25">
       <c r="B195" s="1"/>
-      <c r="D195" s="15" t="s">
+      <c r="D195" s="14" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="196" ht="14.25">
       <c r="B196" s="1"/>
-      <c r="D196" s="15" t="s">
+      <c r="D196" s="14" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="197" ht="14.25">
       <c r="B197" s="1"/>
-      <c r="D197" s="15" t="s">
+      <c r="D197" s="14" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="198" ht="14.25">
       <c r="B198" s="1"/>
-      <c r="D198" s="15" t="s">
+      <c r="D198" s="14" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="199" ht="14.25">
       <c r="B199" s="1"/>
-      <c r="D199" s="15" t="s">
+      <c r="D199" s="14" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="200" ht="14.25">
       <c r="B200" s="1"/>
-      <c r="D200" s="15" t="s">
+      <c r="D200" s="14" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="201" ht="14.25">
       <c r="B201" s="1"/>
-      <c r="D201" s="15" t="s">
+      <c r="D201" s="14" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="202" ht="14.25">
       <c r="B202" s="1"/>
-      <c r="D202" s="15" t="s">
+      <c r="D202" s="14" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="203" ht="14.25">
       <c r="B203" s="1"/>
-      <c r="D203" s="15" t="s">
+      <c r="D203" s="14" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="204" ht="14.25">
       <c r="B204" s="1"/>
-      <c r="D204" s="15" t="s">
+      <c r="D204" s="14" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="205" ht="14.25">
       <c r="B205" s="1"/>
-      <c r="D205" s="15" t="s">
+      <c r="D205" s="14" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="206" ht="14.25">
       <c r="B206" s="1"/>
-      <c r="D206" s="15" t="s">
+      <c r="D206" s="14" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="207" ht="14.25">
       <c r="B207" s="1"/>
-      <c r="D207" s="15" t="s">
+      <c r="D207" s="14" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="208" ht="14.25">
       <c r="B208" s="1"/>
-      <c r="D208" s="15" t="s">
+      <c r="D208" s="14" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="209" ht="14.25">
       <c r="B209" s="1"/>
-      <c r="D209" s="15" t="s">
+      <c r="D209" s="14" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="210" ht="14.25">
       <c r="B210" s="1"/>
-      <c r="D210" s="15" t="s">
+      <c r="D210" s="14" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="211" ht="14.25">
       <c r="B211" s="1"/>
-      <c r="D211" s="15" t="s">
+      <c r="D211" s="14" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="212" ht="14.25">
       <c r="B212" s="1"/>
-      <c r="D212" s="15" t="s">
+      <c r="D212" s="14" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="213" ht="14.25">
       <c r="B213" s="1"/>
-      <c r="D213" s="15" t="s">
+      <c r="D213" s="14" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="214" ht="14.25">
       <c r="B214" s="1"/>
-      <c r="D214" s="15" t="s">
+      <c r="D214" s="14" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="215" ht="14.25">
       <c r="B215" s="1"/>
-      <c r="D215" s="15" t="s">
+      <c r="D215" s="14" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="216" ht="14.25">
       <c r="B216" s="1"/>
-      <c r="D216" s="15" t="s">
+      <c r="D216" s="14" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="217" ht="14.25">
       <c r="B217" s="1"/>
-      <c r="D217" s="15" t="s">
+      <c r="D217" s="14" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="218" ht="14.25">
       <c r="B218" s="1"/>
-      <c r="D218" s="15" t="s">
+      <c r="D218" s="14" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="219" ht="14.25">
       <c r="B219" s="1"/>
-      <c r="D219" s="15" t="s">
+      <c r="D219" s="14" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="220" ht="14.25">
       <c r="B220" s="1"/>
-      <c r="D220" s="15" t="s">
+      <c r="D220" s="14" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="221" ht="14.25">
       <c r="B221" s="1"/>
-      <c r="D221" s="15" t="s">
+      <c r="D221" s="14" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="222" ht="14.25">
       <c r="B222" s="1"/>
-      <c r="D222" s="15" t="s">
+      <c r="D222" s="14" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="223" ht="14.25">
       <c r="B223" s="1"/>
-      <c r="D223" s="15" t="s">
+      <c r="D223" s="14" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="224" ht="14.25">
       <c r="B224" s="1"/>
-      <c r="D224" s="15" t="s">
+      <c r="D224" s="14" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="225" ht="14.25">
       <c r="B225" s="1"/>
-      <c r="D225" s="15" t="s">
+      <c r="D225" s="14" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="226" ht="14.25">
       <c r="B226" s="1"/>
-      <c r="D226" s="15" t="s">
+      <c r="D226" s="14" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="227" ht="14.25">
       <c r="B227" s="1"/>
-      <c r="D227" s="15" t="s">
+      <c r="D227" s="14" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="228" ht="14.25">
       <c r="B228" s="1"/>
-      <c r="D228" s="15" t="s">
+      <c r="D228" s="14" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="229" ht="14.25">
       <c r="B229" s="1"/>
-      <c r="D229" s="15" t="s">
+      <c r="D229" s="14" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="230" ht="14.25">
       <c r="B230" s="1"/>
-      <c r="D230" s="15" t="s">
+      <c r="D230" s="14" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="231" ht="14.25">
       <c r="B231" s="1"/>
-      <c r="D231" s="15" t="s">
+      <c r="D231" s="14" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="232" ht="14.25">
       <c r="B232" s="1"/>
-      <c r="D232" s="15" t="s">
+      <c r="D232" s="14" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="233" ht="14.25">
       <c r="B233" s="1"/>
-      <c r="D233" s="15" t="s">
+      <c r="D233" s="14" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="234" ht="14.25">
       <c r="B234" s="1"/>
-      <c r="D234" s="15" t="s">
+      <c r="D234" s="14" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="235" ht="14.25">
       <c r="B235" s="1"/>
-      <c r="D235" s="15" t="s">
+      <c r="D235" s="14" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="236" ht="14.25">
       <c r="B236" s="1"/>
-      <c r="D236" s="15" t="s">
+      <c r="D236" s="14" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="237" ht="14.25">
       <c r="B237" s="1"/>
-      <c r="D237" s="15" t="s">
+      <c r="D237" s="14" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="238" ht="14.25">
       <c r="B238" s="1"/>
-      <c r="D238" s="15" t="s">
+      <c r="D238" s="14" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="239" ht="14.25">
       <c r="B239" s="1"/>
-      <c r="D239" s="15" t="s">
+      <c r="D239" s="14" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="240" ht="14.25">
       <c r="B240" s="1"/>
-      <c r="D240" s="15" t="s">
+      <c r="D240" s="14" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="241" ht="14.25">
       <c r="B241" s="1"/>
-      <c r="D241" s="15" t="s">
+      <c r="D241" s="14" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="242" ht="14.25">
       <c r="B242" s="1"/>
-      <c r="D242" s="15" t="s">
+      <c r="D242" s="14" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="243" ht="14.25">
       <c r="B243" s="1"/>
-      <c r="D243" s="15" t="s">
+      <c r="D243" s="14" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="244" ht="14.25">
       <c r="B244" s="1"/>
-      <c r="D244" s="15" t="s">
+      <c r="D244" s="14" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="245" ht="14.25">
       <c r="B245" s="1"/>
-      <c r="D245" s="15" t="s">
+      <c r="D245" s="14" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="246" ht="14.25">
       <c r="B246" s="1"/>
-      <c r="D246" s="15" t="s">
+      <c r="D246" s="14" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="247" ht="14.25">
       <c r="B247" s="1"/>
-      <c r="D247" s="15" t="s">
+      <c r="D247" s="14" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="248" ht="14.25">
       <c r="B248" s="1"/>
-      <c r="D248" s="15" t="s">
+      <c r="D248" s="14" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="249" ht="14.25">
       <c r="B249" s="1"/>
-      <c r="D249" s="15" t="s">
+      <c r="D249" s="14" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="250" ht="14.25">
       <c r="B250" s="1"/>
-      <c r="D250" s="15" t="s">
+      <c r="D250" s="14" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="251" ht="14.25">
       <c r="B251" s="1"/>
-      <c r="D251" s="15" t="s">
+      <c r="D251" s="14" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="252" ht="14.25">
       <c r="B252" s="1"/>
-      <c r="D252" s="15" t="s">
+      <c r="D252" s="14" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="253" ht="14.25">
       <c r="B253" s="1"/>
-      <c r="D253" s="15" t="s">
+      <c r="D253" s="14" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="254" ht="14.25">
       <c r="B254" s="1"/>
-      <c r="D254" s="15" t="s">
+      <c r="D254" s="14" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="255" ht="14.25">
       <c r="B255" s="1"/>
-      <c r="D255" s="15" t="s">
+      <c r="D255" s="14" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="256" ht="14.25">
       <c r="B256" s="1"/>
-      <c r="D256" s="15" t="s">
+      <c r="D256" s="14" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="257" ht="14.25">
       <c r="B257" s="1"/>
-      <c r="D257" s="15" t="s">
+      <c r="D257" s="14" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="258" ht="14.25">
       <c r="B258" s="1"/>
-      <c r="D258" s="15" t="s">
+      <c r="D258" s="14" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="259" ht="14.25">
       <c r="B259" s="1"/>
-      <c r="D259" s="15" t="s">
+      <c r="D259" s="14" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="260" ht="14.25">
       <c r="B260" s="1"/>
-      <c r="D260" s="15" t="s">
+      <c r="D260" s="14" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="261" ht="14.25">
       <c r="B261" s="1"/>
-      <c r="D261" s="15" t="s">
+      <c r="D261" s="14" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="262" ht="14.25">
       <c r="B262" s="1"/>
-      <c r="D262" s="15" t="s">
+      <c r="D262" s="14" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="263" ht="14.25">
       <c r="B263" s="1"/>
-      <c r="D263" s="15" t="s">
+      <c r="D263" s="14" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="264" ht="14.25">
       <c r="B264" s="1"/>
-      <c r="D264" s="15" t="s">
+      <c r="D264" s="14" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="265" ht="14.25">
       <c r="B265" s="1"/>
-      <c r="D265" s="15" t="s">
+      <c r="D265" s="14" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="266" ht="14.25">
       <c r="B266" s="1"/>
-      <c r="D266" s="15" t="s">
+      <c r="D266" s="14" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="267" ht="14.25">
       <c r="B267" s="1"/>
-      <c r="D267" s="15" t="s">
+      <c r="D267" s="14" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="268" ht="14.25">
       <c r="B268" s="1"/>
-      <c r="D268" s="15" t="s">
+      <c r="D268" s="14" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="269" ht="14.25">
       <c r="B269" s="1"/>
-      <c r="D269" s="15" t="s">
+      <c r="D269" s="14" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="270" ht="14.25">
       <c r="B270" s="1"/>
-      <c r="D270" s="15" t="s">
+      <c r="D270" s="14" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="271" ht="14.25">
       <c r="B271" s="1"/>
-      <c r="D271" s="15" t="s">
+      <c r="D271" s="14" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="272" ht="14.25">
       <c r="B272" s="1"/>
-      <c r="D272" s="15" t="s">
+      <c r="D272" s="14" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="273" ht="14.25">
       <c r="B273" s="1"/>
-      <c r="D273" s="15" t="s">
+      <c r="D273" s="14" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="274" ht="14.25">
       <c r="B274" s="1"/>
-      <c r="D274" s="15" t="s">
+      <c r="D274" s="14" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="275" ht="14.25">
       <c r="B275" s="1"/>
-      <c r="D275" s="15" t="s">
+      <c r="D275" s="14" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="276" ht="14.25">
       <c r="B276" s="1"/>
-      <c r="D276" s="15" t="s">
+      <c r="D276" s="14" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="277" ht="14.25">
       <c r="B277" s="1"/>
-      <c r="D277" s="15" t="s">
+      <c r="D277" s="14" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="278" ht="14.25">
       <c r="B278" s="1"/>
-      <c r="D278" s="15" t="s">
+      <c r="D278" s="14" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="279" ht="14.25">
       <c r="B279" s="1"/>
-      <c r="D279" s="15" t="s">
+      <c r="D279" s="14" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="280" ht="14.25">
       <c r="B280" s="1"/>
-      <c r="D280" s="15" t="s">
+      <c r="D280" s="14" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="281" ht="14.25">
       <c r="B281" s="1"/>
-      <c r="D281" s="15" t="s">
+      <c r="D281" s="14" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="282" ht="14.25">
       <c r="B282" s="1"/>
-      <c r="D282" s="15" t="s">
+      <c r="D282" s="14" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="283" ht="14.25">
       <c r="B283" s="1"/>
-      <c r="D283" s="15" t="s">
+      <c r="D283" s="14" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="284" ht="14.25">
       <c r="B284" s="1"/>
-      <c r="D284" s="15" t="s">
+      <c r="D284" s="14" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="285" ht="14.25">
       <c r="B285" s="1"/>
-      <c r="D285" s="15" t="s">
+      <c r="D285" s="14" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="286" ht="14.25">
       <c r="B286" s="1"/>
-      <c r="D286" s="15" t="s">
+      <c r="D286" s="14" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="287" ht="14.25">
       <c r="B287" s="1"/>
-      <c r="D287" s="15" t="s">
+      <c r="D287" s="14" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="288" ht="14.25">
       <c r="B288" s="1"/>
-      <c r="D288" s="15" t="s">
+      <c r="D288" s="14" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="289" ht="14.25">
       <c r="B289" s="1"/>
-      <c r="D289" s="15" t="s">
+      <c r="D289" s="14" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="290" ht="14.25">
       <c r="B290" s="1"/>
-      <c r="D290" s="15" t="s">
+      <c r="D290" s="14" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="291" ht="14.25">
       <c r="B291" s="1"/>
-      <c r="D291" s="15" t="s">
+      <c r="D291" s="14" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="292" ht="14.25">
       <c r="B292" s="1"/>
-      <c r="D292" s="15" t="s">
+      <c r="D292" s="14" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="293" ht="14.25">
       <c r="B293" s="1"/>
-      <c r="D293" s="15" t="s">
+      <c r="D293" s="14" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="294" ht="14.25">
       <c r="B294" s="1"/>
-      <c r="D294" s="15" t="s">
+      <c r="D294" s="14" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="295" ht="14.25">
       <c r="B295" s="1"/>
-      <c r="D295" s="15" t="s">
+      <c r="D295" s="14" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="296" ht="14.25">
       <c r="B296" s="1"/>
-      <c r="D296" s="15" t="s">
+      <c r="D296" s="14" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="297" ht="14.25">
       <c r="B297" s="1"/>
-      <c r="D297" s="15" t="s">
+      <c r="D297" s="14" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="298" ht="14.25">
       <c r="B298" s="1"/>
-      <c r="D298" s="15" t="s">
+      <c r="D298" s="14" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="299" ht="14.25">
       <c r="B299" s="1"/>
-      <c r="D299" s="15" t="s">
+      <c r="D299" s="14" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="300" ht="14.25">
       <c r="B300" s="1"/>
-      <c r="D300" s="15" t="s">
+      <c r="D300" s="14" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="301" ht="14.25">
       <c r="B301" s="1"/>
-      <c r="D301" s="15" t="s">
+      <c r="D301" s="14" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="302" ht="14.25">
       <c r="B302" s="1"/>
-      <c r="D302" s="15" t="s">
+      <c r="D302" s="14" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="303" ht="14.25">
       <c r="B303" s="1"/>
-      <c r="D303" s="15" t="s">
+      <c r="D303" s="14" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="304" ht="14.25">
       <c r="B304" s="1"/>
-      <c r="D304" s="15" t="s">
+      <c r="D304" s="14" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="305" ht="14.25">
       <c r="B305" s="1"/>
-      <c r="D305" s="15" t="s">
+      <c r="D305" s="14" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="306" ht="14.25">
       <c r="B306" s="1"/>
-      <c r="D306" s="15" t="s">
+      <c r="D306" s="14" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="307" ht="14.25">
       <c r="B307" s="1"/>
-      <c r="D307" s="15" t="s">
+      <c r="D307" s="14" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="308" ht="14.25">
       <c r="B308" s="1"/>
-      <c r="D308" s="15" t="s">
+      <c r="D308" s="14" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="309" ht="14.25">
       <c r="B309" s="1"/>
-      <c r="D309" s="15" t="s">
+      <c r="D309" s="14" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="310" ht="14.25">
       <c r="B310" s="1"/>
-      <c r="D310" s="15" t="s">
+      <c r="D310" s="14" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="311" ht="14.25">
       <c r="B311" s="1"/>
-      <c r="D311" s="15" t="s">
+      <c r="D311" s="14" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="312" ht="14.25">
       <c r="B312" s="1"/>
-      <c r="D312" s="15" t="s">
+      <c r="D312" s="14" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="313" ht="14.25">
       <c r="B313" s="1"/>
-      <c r="D313" s="15" t="s">
+      <c r="D313" s="14" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="314" ht="14.25">
       <c r="B314" s="1"/>
-      <c r="D314" s="15" t="s">
+      <c r="D314" s="14" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="315" ht="14.25">
       <c r="B315" s="1"/>
-      <c r="D315" s="15" t="s">
+      <c r="D315" s="14" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="316" ht="14.25">
       <c r="B316" s="1"/>
-      <c r="D316" s="15" t="s">
+      <c r="D316" s="14" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="317" ht="14.25">
       <c r="B317" s="1"/>
-      <c r="D317" s="15" t="s">
+      <c r="D317" s="14" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="318" ht="14.25">
       <c r="B318" s="1"/>
-      <c r="D318" s="15" t="s">
+      <c r="D318" s="14" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="319" ht="14.25">
       <c r="B319" s="1"/>
-      <c r="D319" s="15" t="s">
+      <c r="D319" s="14" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="320" ht="14.25">
       <c r="B320" s="1"/>
-      <c r="D320" s="15" t="s">
+      <c r="D320" s="14" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="321" ht="14.25">
       <c r="B321" s="1"/>
-      <c r="D321" s="15" t="s">
+      <c r="D321" s="14" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="322" ht="14.25">
       <c r="B322" s="1"/>
-      <c r="D322" s="15" t="s">
+      <c r="D322" s="14" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="323" ht="14.25">
       <c r="B323" s="1"/>
-      <c r="D323" s="15" t="s">
+      <c r="D323" s="14" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="324" ht="14.25">
       <c r="B324" s="1"/>
-      <c r="D324" s="15" t="s">
+      <c r="D324" s="14" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="325" ht="14.25">
       <c r="B325" s="1"/>
-      <c r="D325" s="15" t="s">
+      <c r="D325" s="14" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="326" ht="14.25">
       <c r="B326" s="1"/>
-      <c r="D326" s="15" t="s">
+      <c r="D326" s="14" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="327" ht="14.25">
       <c r="B327" s="1"/>
-      <c r="D327" s="15" t="s">
+      <c r="D327" s="14" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="328" ht="14.25">
       <c r="B328" s="1"/>
-      <c r="D328" s="15" t="s">
+      <c r="D328" s="14" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="329" ht="14.25">
       <c r="B329" s="1"/>
-      <c r="D329" s="15" t="s">
+      <c r="D329" s="14" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="330" ht="14.25">
       <c r="B330" s="1"/>
-      <c r="D330" s="15" t="s">
+      <c r="D330" s="14" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="331" ht="14.25">
       <c r="B331" s="1"/>
-      <c r="D331" s="15" t="s">
+      <c r="D331" s="14" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="332" ht="14.25">
       <c r="B332" s="1"/>
-      <c r="D332" s="15" t="s">
+      <c r="D332" s="14" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="333" ht="14.25">
       <c r="B333" s="1"/>
-      <c r="D333" s="15" t="s">
+      <c r="D333" s="14" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="334" ht="14.25">
       <c r="B334" s="1"/>
-      <c r="D334" s="15" t="s">
+      <c r="D334" s="14" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="335" ht="14.25">
       <c r="B335" s="1"/>
-      <c r="D335" s="15" t="s">
+      <c r="D335" s="14" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="336" ht="14.25">
       <c r="B336" s="1"/>
-      <c r="D336" s="15" t="s">
+      <c r="D336" s="14" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="337" ht="14.25">
       <c r="B337" s="1"/>
-      <c r="D337" s="15" t="s">
+      <c r="D337" s="14" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="338" ht="14.25">
       <c r="B338" s="1"/>
-      <c r="D338" s="15" t="s">
+      <c r="D338" s="14" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="339" ht="14.25">
       <c r="B339" s="1"/>
-      <c r="D339" s="15" t="s">
+      <c r="D339" s="14" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="340" ht="14.25">
       <c r="B340" s="1"/>
-      <c r="D340" s="15" t="s">
+      <c r="D340" s="14" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="341" ht="14.25">
       <c r="B341" s="1"/>
-      <c r="D341" s="15" t="s">
+      <c r="D341" s="14" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="342" ht="14.25">
       <c r="B342" s="1"/>
-      <c r="D342" s="15" t="s">
+      <c r="D342" s="14" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="343" ht="14.25">
       <c r="B343" s="1"/>
-      <c r="D343" s="15" t="s">
+      <c r="D343" s="14" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="344" ht="14.25">
       <c r="B344" s="1"/>
-      <c r="D344" s="15" t="s">
+      <c r="D344" s="14" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="345" ht="14.25">
       <c r="B345" s="1"/>
-      <c r="D345" s="15" t="s">
+      <c r="D345" s="14" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="346" ht="14.25">
       <c r="B346" s="1"/>
-      <c r="D346" s="15" t="s">
+      <c r="D346" s="14" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="347" ht="14.25">
       <c r="B347" s="1"/>
-      <c r="D347" s="15" t="s">
+      <c r="D347" s="14" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="348" ht="14.25">
       <c r="B348" s="1"/>
-      <c r="D348" s="15" t="s">
+      <c r="D348" s="14" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="349" ht="14.25">
       <c r="B349" s="1"/>
-      <c r="D349" s="15" t="s">
+      <c r="D349" s="14" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="350" ht="14.25">
       <c r="B350" s="1"/>
-      <c r="D350" s="15" t="s">
+      <c r="D350" s="14" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="351" ht="14.25">
       <c r="B351" s="1"/>
-      <c r="D351" s="15" t="s">
+      <c r="D351" s="14" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="352" ht="14.25">
       <c r="B352" s="1"/>
-      <c r="D352" s="15" t="s">
+      <c r="D352" s="14" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="353" ht="14.25">
       <c r="B353" s="1"/>
-      <c r="D353" s="15" t="s">
+      <c r="D353" s="14" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="354" ht="14.25">
       <c r="B354" s="1"/>
-      <c r="D354" s="15" t="s">
+      <c r="D354" s="14" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="355" ht="14.25">
       <c r="B355" s="1"/>
-      <c r="D355" s="15" t="s">
+      <c r="D355" s="14" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="356" ht="14.25">
       <c r="B356" s="1"/>
-      <c r="D356" s="15" t="s">
+      <c r="D356" s="14" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="357" ht="14.25">
       <c r="B357" s="1"/>
-      <c r="D357" s="15" t="s">
+      <c r="D357" s="14" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="358" ht="14.25">
       <c r="B358" s="1"/>
-      <c r="D358" s="15" t="s">
+      <c r="D358" s="14" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="359" ht="14.25">
       <c r="B359" s="1"/>
-      <c r="D359" s="15" t="s">
+      <c r="D359" s="14" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="360" ht="14.25">
       <c r="B360" s="1"/>
-      <c r="D360" s="15" t="s">
+      <c r="D360" s="14" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="361" ht="14.25">
       <c r="B361" s="1"/>
-      <c r="D361" s="15" t="s">
+      <c r="D361" s="14" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="362" ht="14.25">
       <c r="B362" s="1"/>
-      <c r="D362" s="15" t="s">
+      <c r="D362" s="14" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="363" ht="14.25">
       <c r="B363" s="1"/>
-      <c r="D363" s="15" t="s">
+      <c r="D363" s="14" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="364" ht="14.25">
       <c r="B364" s="1"/>
-      <c r="D364" s="15" t="s">
+      <c r="D364" s="14" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="365" ht="14.25">
       <c r="B365" s="1"/>
-      <c r="D365" s="15" t="s">
+      <c r="D365" s="14" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="366" ht="14.25">
       <c r="B366" s="1"/>
-      <c r="D366" s="15" t="s">
+      <c r="D366" s="14" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="367" ht="14.25">
       <c r="B367" s="1"/>
-      <c r="D367" s="15" t="s">
+      <c r="D367" s="14" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="368" ht="14.25">
       <c r="B368" s="1"/>
-      <c r="D368" s="15" t="s">
+      <c r="D368" s="14" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="369" ht="14.25">
       <c r="B369" s="1"/>
-      <c r="D369" s="15" t="s">
+      <c r="D369" s="14" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="370" ht="14.25">
       <c r="B370" s="1"/>
-      <c r="D370" s="15" t="s">
+      <c r="D370" s="14" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="371" ht="14.25">
       <c r="B371" s="1"/>
-      <c r="D371" s="15" t="s">
+      <c r="D371" s="14" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="372" ht="14.25">
       <c r="B372" s="1"/>
-      <c r="D372" s="15" t="s">
+      <c r="D372" s="14" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="373" ht="14.25">
       <c r="B373" s="1"/>
-      <c r="D373" s="15" t="s">
+      <c r="D373" s="14" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="374" ht="14.25">
       <c r="B374" s="1"/>
-      <c r="D374" s="15" t="s">
+      <c r="D374" s="14" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="375" ht="14.25">
       <c r="B375" s="1"/>
-      <c r="D375" s="15" t="s">
+      <c r="D375" s="14" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="376" ht="14.25">
       <c r="B376" s="1"/>
-      <c r="D376" s="15" t="s">
+      <c r="D376" s="14" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="377" ht="14.25">
       <c r="B377" s="1"/>
-      <c r="D377" s="15" t="s">
+      <c r="D377" s="14" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="378" ht="14.25">
       <c r="B378" s="1"/>
-      <c r="D378" s="15" t="s">
+      <c r="D378" s="14" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="379" ht="14.25">
       <c r="B379" s="1"/>
-      <c r="D379" s="15" t="s">
+      <c r="D379" s="14" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="380" ht="14.25">
       <c r="B380" s="1"/>
-      <c r="D380" s="15" t="s">
+      <c r="D380" s="14" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="381" ht="14.25">
       <c r="B381" s="1"/>
-      <c r="D381" s="15" t="s">
+      <c r="D381" s="14" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="382" ht="14.25">
       <c r="B382" s="1"/>
-      <c r="D382" s="15" t="s">
+      <c r="D382" s="14" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="383" ht="14.25">
       <c r="B383" s="1"/>
-      <c r="D383" s="15" t="s">
+      <c r="D383" s="14" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="384" ht="14.25">
       <c r="B384" s="1"/>
-      <c r="D384" s="15" t="s">
+      <c r="D384" s="14" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="385" ht="14.25">
       <c r="B385" s="1"/>
-      <c r="D385" s="15" t="s">
+      <c r="D385" s="14" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="386" ht="14.25">
       <c r="B386" s="1"/>
-      <c r="D386" s="15" t="s">
+      <c r="D386" s="14" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="387" ht="14.25">
       <c r="B387" s="1"/>
-      <c r="D387" s="15" t="s">
+      <c r="D387" s="14" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="388" ht="14.25">
       <c r="B388" s="1"/>
-      <c r="D388" s="15" t="s">
+      <c r="D388" s="14" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="389" ht="14.25">
       <c r="B389" s="1"/>
-      <c r="D389" s="15" t="s">
+      <c r="D389" s="14" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="390" ht="14.25">
       <c r="B390" s="1"/>
-      <c r="D390" s="15" t="s">
+      <c r="D390" s="14" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="391" ht="14.25">
       <c r="B391" s="1"/>
-      <c r="D391" s="15" t="s">
+      <c r="D391" s="14" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="392" ht="14.25">
       <c r="B392" s="1"/>
-      <c r="D392" s="15" t="s">
+      <c r="D392" s="14" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="393" ht="14.25">
       <c r="B393" s="1"/>
-      <c r="D393" s="15" t="s">
+      <c r="D393" s="14" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="394" ht="14.25">
       <c r="B394" s="1"/>
-      <c r="D394" s="15" t="s">
+      <c r="D394" s="14" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="395" ht="14.25">
       <c r="B395" s="1"/>
-      <c r="D395" s="15" t="s">
+      <c r="D395" s="14" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="396" ht="14.25">
       <c r="B396" s="1"/>
-      <c r="D396" s="15" t="s">
+      <c r="D396" s="14" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="397" ht="14.25">
       <c r="B397" s="1"/>
-      <c r="D397" s="15" t="s">
+      <c r="D397" s="14" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="398" ht="14.25">
       <c r="B398" s="1"/>
-      <c r="D398" s="15" t="s">
+      <c r="D398" s="14" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="399" ht="14.25">
       <c r="B399" s="1"/>
-      <c r="D399" s="15" t="s">
+      <c r="D399" s="14" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="400" ht="14.25">
       <c r="B400" s="1"/>
-      <c r="D400" s="15" t="s">
+      <c r="D400" s="14" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="401" ht="14.25">
       <c r="B401" s="1"/>
-      <c r="D401" s="15" t="s">
+      <c r="D401" s="14" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="402" ht="14.25">
       <c r="B402" s="1"/>
-      <c r="D402" s="15" t="s">
+      <c r="D402" s="14" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="403" ht="14.25">
       <c r="B403" s="1"/>
-      <c r="D403" s="15" t="s">
+      <c r="D403" s="14" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="404" ht="14.25">
       <c r="B404" s="1"/>
-      <c r="D404" s="15" t="s">
+      <c r="D404" s="14" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="405" ht="14.25">
       <c r="B405" s="1"/>
-      <c r="D405" s="15" t="s">
+      <c r="D405" s="14" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="406" ht="14.25">
       <c r="B406" s="1"/>
-      <c r="D406" s="15" t="s">
+      <c r="D406" s="14" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="407" ht="14.25">
       <c r="B407" s="1"/>
-      <c r="D407" s="15" t="s">
+      <c r="D407" s="14" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="408" ht="14.25">
       <c r="B408" s="1"/>
-      <c r="D408" s="15" t="s">
+      <c r="D408" s="14" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="409" ht="14.25">
       <c r="B409" s="1"/>
-      <c r="D409" s="15" t="s">
+      <c r="D409" s="14" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="410" ht="14.25">
       <c r="B410" s="1"/>
-      <c r="D410" s="15" t="s">
+      <c r="D410" s="14" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="411" ht="14.25">
       <c r="B411" s="1"/>
-      <c r="D411" s="15" t="s">
+      <c r="D411" s="14" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="412" ht="14.25">
       <c r="B412" s="1"/>
-      <c r="D412" s="15" t="s">
+      <c r="D412" s="14" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="413" ht="14.25">
       <c r="B413" s="1"/>
-      <c r="D413" s="15" t="s">
+      <c r="D413" s="14" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="414" ht="14.25">
       <c r="B414" s="1"/>
-      <c r="D414" s="15" t="s">
+      <c r="D414" s="14" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="415" ht="14.25">
       <c r="B415" s="1"/>
-      <c r="D415" s="15" t="s">
+      <c r="D415" s="14" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="416" ht="14.25">
       <c r="B416" s="1"/>
-      <c r="D416" s="15" t="s">
+      <c r="D416" s="14" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="417" ht="14.25">
       <c r="B417" s="1"/>
-      <c r="D417" s="15" t="s">
+      <c r="D417" s="14" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="418" ht="14.25">
       <c r="B418" s="1"/>
-      <c r="D418" s="15" t="s">
+      <c r="D418" s="14" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="419" ht="14.25">
       <c r="B419" s="1"/>
-      <c r="D419" s="15" t="s">
+      <c r="D419" s="14" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="420" ht="14.25">
       <c r="B420" s="1"/>
-      <c r="D420" s="15" t="s">
+      <c r="D420" s="14" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="421" ht="14.25">
       <c r="B421" s="1"/>
-      <c r="D421" s="15" t="s">
+      <c r="D421" s="14" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="422" ht="14.25">
       <c r="B422" s="1"/>
-      <c r="D422" s="15" t="s">
+      <c r="D422" s="14" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="423" ht="14.25">
       <c r="B423" s="1"/>
-      <c r="D423" s="15" t="s">
+      <c r="D423" s="14" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="424" ht="14.25">
       <c r="B424" s="1"/>
-      <c r="D424" s="15" t="s">
+      <c r="D424" s="14" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="425" ht="14.25">
       <c r="B425" s="1"/>
-      <c r="D425" s="15" t="s">
+      <c r="D425" s="14" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="426" ht="14.25">
       <c r="B426" s="1"/>
-      <c r="D426" s="15" t="s">
+      <c r="D426" s="14" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="427" ht="14.25">
       <c r="B427" s="1"/>
-      <c r="D427" s="15" t="s">
+      <c r="D427" s="14" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="428" ht="14.25">
       <c r="B428" s="1"/>
-      <c r="D428" s="15" t="s">
+      <c r="D428" s="14" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="429" ht="14.25">
       <c r="B429" s="1"/>
-      <c r="D429" s="15" t="s">
+      <c r="D429" s="14" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="430" ht="14.25">
       <c r="B430" s="1"/>
-      <c r="D430" s="15" t="s">
+      <c r="D430" s="14" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="431" ht="14.25">
       <c r="B431" s="1"/>
-      <c r="D431" s="15" t="s">
+      <c r="D431" s="14" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="432" ht="14.25">
       <c r="B432" s="1"/>
-      <c r="D432" s="15" t="s">
+      <c r="D432" s="14" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="433" ht="14.25">
-      <c r="D433" s="15" t="s">
+      <c r="D433" s="14" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="434" ht="14.25">
-      <c r="D434" s="15" t="s">
+      <c r="D434" s="14" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="435" ht="14.25">
-      <c r="D435" s="15" t="s">
+      <c r="D435" s="14" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="436" ht="14.25">
-      <c r="D436" s="15" t="s">
+      <c r="D436" s="14" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="437" ht="14.25">
-      <c r="D437" s="15" t="s">
+      <c r="D437" s="14" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="438" ht="14.25">
-      <c r="D438" s="15" t="s">
+      <c r="D438" s="14" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="439" ht="14.25">
-      <c r="D439" s="15" t="s">
+      <c r="D439" s="14" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="440" ht="14.25">
-      <c r="D440" s="15" t="s">
+      <c r="D440" s="14" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="441" ht="14.25">
-      <c r="D441" s="15" t="s">
+      <c r="D441" s="14" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="442" ht="14.25">
-      <c r="D442" s="15" t="s">
+      <c r="D442" s="14" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="443" ht="14.25">
-      <c r="D443" s="15" t="s">
+      <c r="D443" s="14" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="444" ht="14.25">
-      <c r="D444" s="15" t="s">
+      <c r="D444" s="14" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="445" ht="14.25">
-      <c r="D445" s="15" t="s">
+      <c r="D445" s="14" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="446" ht="14.25">
-      <c r="D446" s="15" t="s">
+      <c r="D446" s="14" t="s">
         <v>638</v>
       </c>
     </row>
     <row r="447" ht="14.25">
-      <c r="D447" s="15" t="s">
+      <c r="D447" s="14" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="448" ht="14.25">
-      <c r="D448" s="15" t="s">
+      <c r="D448" s="14" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="449" ht="14.25">
-      <c r="D449" s="15" t="s">
+      <c r="D449" s="14" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="450" ht="14.25">
-      <c r="D450" s="15" t="s">
+      <c r="D450" s="14" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="451" ht="14.25">
-      <c r="D451" s="15" t="s">
+      <c r="D451" s="14" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="452" ht="14.25">
-      <c r="D452" s="15" t="s">
+      <c r="D452" s="14" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="453" ht="14.25">
-      <c r="D453" s="15" t="s">
+      <c r="D453" s="14" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="454" ht="14.25">
-      <c r="D454" s="15" t="s">
+      <c r="D454" s="14" t="s">
         <v>440</v>
       </c>
     </row>
@@ -7301,60 +7333,106 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>641</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>642</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>643</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="D2" s="6"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" style="1" width="26.140625"/>
+    <col customWidth="1" min="2" max="2" style="1" width="26.8515625"/>
+    <col customWidth="1" min="3" max="3" style="1" width="34.7109375"/>
+    <col customWidth="1" min="4" max="4" style="1" width="26.57421875"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="16" customFormat="1">
+      <c r="A1" s="17" t="s">
+        <v>652</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>641</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>653</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>655</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>656</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>657</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
